--- a/du-lieu/OM4-DE-IS-0001.xlsx
+++ b/du-lieu/OM4-DE-IS-0001.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{2C616905-91AD-40A3-828F-6445A8A559D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10890" yWindow="-20145" windowWidth="29010" windowHeight="18105" tabRatio="917" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10890" yWindow="-20145" windowWidth="29010" windowHeight="18105" tabRatio="917" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Breakdown CI" sheetId="24" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <sheet name="BL" sheetId="7" r:id="rId10"/>
     <sheet name="PSIC" sheetId="11" r:id="rId11"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId12"/>
-  </externalReferences>
   <definedNames>
     <definedName name="__123Graph_A" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="__123Graph_A" localSheetId="1" hidden="1">#REF!</definedName>
@@ -125,7 +122,7 @@
     <definedName name="_Fill" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Fill" localSheetId="6" hidden="1">#REF!</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breakdown CI'!$B$8:$AA$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breakdown CI'!$B$8:$AB$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed PL'!$B$13:$AH$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SHIPPING MARK(006)'!$A$1:$A$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SHIPPING MARK(007)'!$A$1:$A$20</definedName>
@@ -221,7 +218,7 @@
     <definedName name="SM" localSheetId="6" hidden="1">#REF!</definedName>
     <definedName name="SM" hidden="1">#REF!</definedName>
     <definedName name="tube_test_press1_12">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Breakdown CI'!$A$1:$N$63</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Breakdown CI'!$A$1:$O$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Detailed PL'!$A$1:$V$69</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'PL(2_2)'!$B$1:$T$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'SHIPPING MARK(006)'!$A$1:$J$20</definedName>
@@ -345,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="221">
   <si>
     <t>OM4-DE-IS-0001</t>
     <phoneticPr fontId="25" type="noConversion"/>
@@ -1400,6 +1397,12 @@
   <si>
     <t>OM4-DE-IS-0001-003</t>
     <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vị Trí</t>
+  </si>
+  <si>
+    <t>S1</t>
   </si>
 </sst>
 </file>
@@ -1982,7 +1985,7 @@
     </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2532,6 +2535,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2568,6 +2574,42 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2592,41 +2634,8 @@
     <xf numFmtId="14" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2645,9 +2654,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2745,13 +2751,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>3969</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>1503826</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>282734</xdr:rowOff>
@@ -2805,13 +2811,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>135890</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>457462</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>93662</xdr:rowOff>
@@ -2847,6 +2853,61 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3969</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1503826" cy="278765"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EE2E9C8-4729-6A4A-BEE8-35DD361DE31D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="9117" b="11386"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="677333" y="118269"/>
+          <a:ext cx="1503826" cy="278765"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3264,133 +3325,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Commercial Invoice"/>
-      <sheetName val="Breakdown CI"/>
-      <sheetName val="Packing List (1_2)"/>
-      <sheetName val="PL(2_2)"/>
-      <sheetName val="Detailed PL"/>
-      <sheetName val="SHIPPING MARK(001)"/>
-      <sheetName val="SHIPPING MARK(002)"/>
-      <sheetName val="SHIPPING MARK(003)"/>
-      <sheetName val="SHIPPING MARK(004)"/>
-      <sheetName val="SHIPPING MARK(005)"/>
-      <sheetName val="SHIPPING MARK(006)"/>
-      <sheetName val="SHIPPING MARK(007)"/>
-      <sheetName val="SHIPPING MARK(008)"/>
-      <sheetName val="SHIPPING MARK(009)"/>
-      <sheetName val="Technical Description"/>
-      <sheetName val="CO"/>
-      <sheetName val="CQ"/>
-      <sheetName val="BL"/>
-      <sheetName val="PSIC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3">
-        <row r="16">
-          <cell r="D16" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F16">
-            <v>1</v>
-          </cell>
-          <cell r="G16" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F17">
-            <v>1</v>
-          </cell>
-          <cell r="G17" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="D18" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F18">
-            <v>1</v>
-          </cell>
-          <cell r="G18" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F19">
-            <v>1</v>
-          </cell>
-          <cell r="G19" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F20">
-            <v>1</v>
-          </cell>
-          <cell r="G20" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F21">
-            <v>1</v>
-          </cell>
-          <cell r="G21" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="D22" t="str">
-            <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
-          </cell>
-          <cell r="F22">
-            <v>1</v>
-          </cell>
-          <cell r="G22" t="str">
-            <v>PKG</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3712,56 +3646,57 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.05078125" style="32" customWidth="1"/>
     <col min="2" max="2" width="3.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="21.1640625" style="42" customWidth="1"/>
-    <col min="4" max="4" width="23.73828125" style="54" customWidth="1"/>
-    <col min="5" max="6" width="21.75" style="54" customWidth="1"/>
-    <col min="7" max="7" width="9.703125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="5.26171875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="5.26171875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="7.6015625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.8203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.9921875" style="6" customWidth="1"/>
-    <col min="13" max="13" width="12.74609375" style="6" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" style="56" customWidth="1"/>
-    <col min="15" max="15" width="1.05078125" style="30" customWidth="1"/>
-    <col min="16" max="18" width="8.76953125" style="31" customWidth="1"/>
-    <col min="19" max="19" width="11.2265625" style="31" customWidth="1"/>
-    <col min="20" max="22" width="8.76953125" style="31" customWidth="1"/>
-    <col min="23" max="28" width="8.76953125" style="32" customWidth="1"/>
-    <col min="29" max="33" width="8.76953125" style="31"/>
-    <col min="34" max="16384" width="8.76953125" style="32"/>
+    <col min="3" max="4" width="21.1640625" style="42" customWidth="1"/>
+    <col min="5" max="5" width="23.73828125" style="54" customWidth="1"/>
+    <col min="6" max="7" width="21.75" style="54" customWidth="1"/>
+    <col min="8" max="8" width="9.703125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="5.26171875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="5.26171875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="7.6015625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="9.8203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.9921875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="12.74609375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" style="56" customWidth="1"/>
+    <col min="16" max="16" width="1.05078125" style="30" customWidth="1"/>
+    <col min="17" max="19" width="8.76953125" style="31" customWidth="1"/>
+    <col min="20" max="20" width="11.2265625" style="31" customWidth="1"/>
+    <col min="21" max="23" width="8.76953125" style="31" customWidth="1"/>
+    <col min="24" max="29" width="8.76953125" style="32" customWidth="1"/>
+    <col min="30" max="34" width="8.76953125" style="31"/>
+    <col min="35" max="16384" width="8.76953125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="9" customHeight="1">
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-    </row>
-    <row r="2" spans="1:33" ht="26.1" customHeight="1">
+    <row r="1" spans="1:34" ht="9" customHeight="1">
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="208"/>
+      <c r="O1" s="208"/>
+    </row>
+    <row r="2" spans="1:34" ht="26.1" customHeight="1">
       <c r="B2" s="29"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="33"/>
+      <c r="G2" s="6"/>
+      <c r="I2" s="6"/>
       <c r="J2" s="33"/>
-      <c r="N2" s="32"/>
+      <c r="K2" s="33"/>
       <c r="O2" s="32"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -3770,25 +3705,26 @@
       <c r="T2" s="32"/>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
-      <c r="AC2" s="32"/>
+      <c r="W2" s="32"/>
       <c r="AD2" s="32"/>
       <c r="AE2" s="32"/>
       <c r="AF2" s="32"/>
       <c r="AG2" s="32"/>
-    </row>
-    <row r="3" spans="1:33" ht="27.6" customHeight="1" thickBot="1">
+      <c r="AH2" s="32"/>
+    </row>
+    <row r="3" spans="1:34" ht="27.6" customHeight="1" thickBot="1">
       <c r="B3" s="29"/>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="183"/>
+      <c r="D3" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="N3" s="32"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
+      <c r="K3" s="209"/>
       <c r="O3" s="32"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -3797,1063 +3733,1129 @@
       <c r="T3" s="32"/>
       <c r="U3" s="32"/>
       <c r="V3" s="32"/>
-      <c r="AC3" s="32"/>
+      <c r="W3" s="32"/>
       <c r="AD3" s="32"/>
       <c r="AE3" s="32"/>
       <c r="AF3" s="32"/>
       <c r="AG3" s="32"/>
-    </row>
-    <row r="4" spans="1:33" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B4" s="197" t="s">
+      <c r="AH3" s="32"/>
+    </row>
+    <row r="4" spans="1:34" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="198"/>
-      <c r="I4" s="198"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="198"/>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="199"/>
-    </row>
-    <row r="5" spans="1:33" s="6" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="212"/>
+    </row>
+    <row r="5" spans="1:34" s="6" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="B5" s="10"/>
       <c r="C5" s="37"/>
-      <c r="D5" s="73"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="10"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="73"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="38"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="41"/>
-      <c r="AC5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="41"/>
       <c r="AD5" s="10"/>
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10"/>
-    </row>
-    <row r="6" spans="1:33" s="6" customFormat="1" ht="14.25">
+      <c r="AH5" s="10"/>
+    </row>
+    <row r="6" spans="1:34" s="6" customFormat="1" ht="14.25">
       <c r="A6" s="9"/>
-      <c r="B6" s="200" t="s">
+      <c r="B6" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="200"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="201"/>
-      <c r="G6" s="201"/>
-      <c r="H6" s="201"/>
-      <c r="I6" s="9" t="s">
+      <c r="G6" s="214"/>
+      <c r="H6" s="214"/>
+      <c r="I6" s="214"/>
+      <c r="J6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="202" t="e">
+      <c r="K6" s="215" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-      <c r="R6" s="6">
+      <c r="L6" s="215"/>
+      <c r="M6" s="215"/>
+      <c r="S6" s="6">
         <v>2</v>
       </c>
-      <c r="S6" s="6">
+      <c r="T6" s="6">
         <v>9817.5</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="6" customFormat="1" ht="17.25" customHeight="1">
+    <row r="7" spans="1:34" s="6" customFormat="1" ht="17.25" customHeight="1">
       <c r="B7" s="10"/>
       <c r="C7" s="37"/>
-      <c r="D7" s="10"/>
+      <c r="D7" s="37"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="125"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="124"/>
       <c r="M7" s="125"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="10"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="41"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
-      <c r="AC7" s="10"/>
+      <c r="W7" s="10"/>
       <c r="AD7" s="10"/>
       <c r="AE7" s="10"/>
       <c r="AF7" s="10"/>
       <c r="AG7" s="10"/>
-    </row>
-    <row r="8" spans="1:33" s="48" customFormat="1" ht="20.25" customHeight="1">
-      <c r="B8" s="203" t="s">
+      <c r="AH7" s="10"/>
+    </row>
+    <row r="8" spans="1:34" s="48" customFormat="1" ht="20.25" customHeight="1">
+      <c r="B8" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="206" t="s">
+      <c r="C8" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="207" t="s">
+      <c r="D8" s="201" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="202" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="208"/>
-      <c r="F8" s="206" t="s">
+      <c r="F8" s="203"/>
+      <c r="G8" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="203" t="s">
+      <c r="H8" s="198" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="211" t="s">
+      <c r="I8" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="212"/>
-      <c r="J8" s="214" t="s">
+      <c r="J8" s="207"/>
+      <c r="K8" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="214" t="s">
+      <c r="L8" s="197" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="214" t="s">
+      <c r="M8" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="214" t="s">
+      <c r="N8" s="197" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="203" t="s">
+      <c r="O8" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="47"/>
+      <c r="P8" s="46"/>
       <c r="Q8" s="47"/>
       <c r="R8" s="47"/>
       <c r="S8" s="47"/>
       <c r="T8" s="47"/>
       <c r="U8" s="47"/>
       <c r="V8" s="47"/>
-      <c r="AC8" s="47"/>
+      <c r="W8" s="47"/>
       <c r="AD8" s="47"/>
       <c r="AE8" s="47"/>
       <c r="AF8" s="47"/>
       <c r="AG8" s="47"/>
-    </row>
-    <row r="9" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="209"/>
-      <c r="E9" s="210"/>
+      <c r="AH8" s="47"/>
+    </row>
+    <row r="9" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="200"/>
+      <c r="E9" s="204"/>
       <c r="F9" s="205"/>
-      <c r="G9" s="204"/>
-      <c r="H9" s="49" t="s">
+      <c r="G9" s="200"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="49" t="s">
+      <c r="J9" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="214"/>
-      <c r="K9" s="214"/>
-      <c r="L9" s="214"/>
-      <c r="M9" s="214"/>
-      <c r="N9" s="204"/>
-      <c r="P9" s="47"/>
+      <c r="K9" s="197"/>
+      <c r="L9" s="197"/>
+      <c r="M9" s="197"/>
+      <c r="N9" s="197"/>
+      <c r="O9" s="199"/>
       <c r="Q9" s="47"/>
       <c r="R9" s="47"/>
       <c r="S9" s="47"/>
       <c r="T9" s="47"/>
       <c r="U9" s="47"/>
       <c r="V9" s="47"/>
-      <c r="AC9" s="47"/>
+      <c r="W9" s="47"/>
       <c r="AD9" s="47"/>
       <c r="AE9" s="47"/>
       <c r="AF9" s="47"/>
       <c r="AG9" s="47"/>
-    </row>
-    <row r="10" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH9" s="47"/>
+    </row>
+    <row r="10" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B10" s="126">
         <v>1</v>
       </c>
       <c r="C10" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="130" t="s">
+      <c r="D10" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="130" t="s">
         <v>212</v>
       </c>
-      <c r="E10" s="131"/>
-      <c r="F10" s="129" t="s">
+      <c r="F10" s="131"/>
+      <c r="G10" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="132" t="s">
+      <c r="H10" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H10" s="133">
+      <c r="I10" s="133">
         <v>1</v>
       </c>
-      <c r="I10" s="133" t="s">
+      <c r="J10" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="134" t="s">
+      <c r="K10" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="140">
+      <c r="L10" s="140">
         <v>2492</v>
       </c>
-      <c r="L10" s="135"/>
-      <c r="M10" s="135">
+      <c r="M10" s="135"/>
+      <c r="N10" s="135">
         <v>15750</v>
       </c>
-      <c r="N10" s="132" t="s">
+      <c r="O10" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="P10" s="47"/>
       <c r="Q10" s="47"/>
       <c r="R10" s="47"/>
       <c r="S10" s="47"/>
       <c r="T10" s="47"/>
       <c r="U10" s="47"/>
       <c r="V10" s="47"/>
-      <c r="AC10" s="47"/>
+      <c r="W10" s="47"/>
       <c r="AD10" s="47"/>
       <c r="AE10" s="47"/>
       <c r="AF10" s="47"/>
       <c r="AG10" s="47"/>
-    </row>
-    <row r="11" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH10" s="47"/>
+    </row>
+    <row r="11" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B11" s="83"/>
       <c r="C11" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="83" t="s">
+      <c r="F11" s="95"/>
+      <c r="G11" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="85" t="s">
+      <c r="H11" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H11" s="174">
+      <c r="I11" s="174">
         <v>20</v>
       </c>
-      <c r="I11" s="174" t="s">
+      <c r="J11" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="170"/>
-      <c r="K11" s="141">
+      <c r="K11" s="170"/>
+      <c r="L11" s="141">
         <v>190</v>
       </c>
-      <c r="L11" s="121">
+      <c r="M11" s="121">
         <v>60</v>
       </c>
-      <c r="M11" s="121">
+      <c r="N11" s="121">
         <v>1200</v>
       </c>
-      <c r="N11" s="85"/>
-      <c r="P11" s="47"/>
+      <c r="O11" s="85"/>
       <c r="Q11" s="47"/>
       <c r="R11" s="47"/>
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
       <c r="U11" s="47"/>
       <c r="V11" s="47"/>
-      <c r="AC11" s="47"/>
+      <c r="W11" s="47"/>
       <c r="AD11" s="47"/>
       <c r="AE11" s="47"/>
       <c r="AF11" s="47"/>
       <c r="AG11" s="47"/>
-    </row>
-    <row r="12" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH11" s="47"/>
+    </row>
+    <row r="12" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B12" s="83"/>
       <c r="C12" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="94" t="s">
+      <c r="D12" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="95"/>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="95"/>
+      <c r="G12" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="85" t="s">
+      <c r="H12" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H12" s="174">
+      <c r="I12" s="174">
         <v>40</v>
       </c>
-      <c r="I12" s="174" t="s">
+      <c r="J12" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="165"/>
-      <c r="K12" s="141">
+      <c r="K12" s="165"/>
+      <c r="L12" s="141">
         <v>916</v>
       </c>
-      <c r="L12" s="121">
+      <c r="M12" s="121">
         <v>144.75</v>
       </c>
-      <c r="M12" s="121">
+      <c r="N12" s="121">
         <v>5790</v>
       </c>
-      <c r="N12" s="85"/>
-      <c r="P12" s="47"/>
+      <c r="O12" s="85"/>
       <c r="Q12" s="47"/>
       <c r="R12" s="47"/>
       <c r="S12" s="47"/>
       <c r="T12" s="47"/>
       <c r="U12" s="47"/>
       <c r="V12" s="47"/>
-      <c r="AC12" s="47"/>
+      <c r="W12" s="47"/>
       <c r="AD12" s="47"/>
       <c r="AE12" s="47"/>
       <c r="AF12" s="47"/>
       <c r="AG12" s="47"/>
-    </row>
-    <row r="13" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH12" s="47"/>
+    </row>
+    <row r="13" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B13" s="83"/>
       <c r="C13" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="94" t="s">
+      <c r="D13" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="95"/>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="95"/>
+      <c r="G13" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="85" t="s">
+      <c r="H13" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H13" s="174">
+      <c r="I13" s="174">
         <v>8</v>
       </c>
-      <c r="I13" s="174" t="s">
+      <c r="J13" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="165"/>
-      <c r="K13" s="141">
+      <c r="K13" s="165"/>
+      <c r="L13" s="141">
         <v>45.6</v>
       </c>
-      <c r="L13" s="121">
+      <c r="M13" s="121">
         <v>36</v>
       </c>
-      <c r="M13" s="121">
+      <c r="N13" s="121">
         <v>288</v>
       </c>
-      <c r="N13" s="85"/>
-      <c r="P13" s="47"/>
+      <c r="O13" s="85"/>
       <c r="Q13" s="47"/>
       <c r="R13" s="47"/>
       <c r="S13" s="47"/>
       <c r="T13" s="47"/>
       <c r="U13" s="47"/>
       <c r="V13" s="47"/>
-      <c r="AC13" s="47"/>
+      <c r="W13" s="47"/>
       <c r="AD13" s="47"/>
       <c r="AE13" s="47"/>
       <c r="AF13" s="47"/>
       <c r="AG13" s="47"/>
-    </row>
-    <row r="14" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH13" s="47"/>
+    </row>
+    <row r="14" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B14" s="83"/>
       <c r="C14" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="94" t="s">
+      <c r="D14" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="95"/>
+      <c r="G14" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="85" t="s">
+      <c r="H14" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H14" s="174">
+      <c r="I14" s="174">
         <v>6</v>
       </c>
-      <c r="I14" s="174" t="s">
+      <c r="J14" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="165"/>
-      <c r="K14" s="141">
+      <c r="K14" s="165"/>
+      <c r="L14" s="141">
         <v>663</v>
       </c>
-      <c r="L14" s="121">
+      <c r="M14" s="121">
         <v>698.5</v>
       </c>
-      <c r="M14" s="121">
+      <c r="N14" s="121">
         <v>4191</v>
       </c>
-      <c r="N14" s="85"/>
-      <c r="P14" s="47"/>
+      <c r="O14" s="85"/>
       <c r="Q14" s="47"/>
       <c r="R14" s="47"/>
       <c r="S14" s="47"/>
       <c r="T14" s="47"/>
       <c r="U14" s="47"/>
       <c r="V14" s="47"/>
-      <c r="AC14" s="47"/>
+      <c r="W14" s="47"/>
       <c r="AD14" s="47"/>
       <c r="AE14" s="47"/>
       <c r="AF14" s="47"/>
       <c r="AG14" s="47"/>
-    </row>
-    <row r="15" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH14" s="47"/>
+    </row>
+    <row r="15" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B15" s="83"/>
       <c r="C15" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="94" t="s">
+      <c r="D15" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="95"/>
-      <c r="F15" s="83" t="s">
+      <c r="F15" s="95"/>
+      <c r="G15" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="85" t="s">
+      <c r="H15" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H15" s="174">
+      <c r="I15" s="174">
         <v>6</v>
       </c>
-      <c r="I15" s="174" t="s">
+      <c r="J15" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="165"/>
-      <c r="K15" s="141">
+      <c r="K15" s="165"/>
+      <c r="L15" s="141">
         <v>7.2</v>
       </c>
-      <c r="L15" s="121">
+      <c r="M15" s="121">
         <v>7.5</v>
       </c>
-      <c r="M15" s="121">
+      <c r="N15" s="121">
         <v>45</v>
       </c>
-      <c r="N15" s="85"/>
-      <c r="P15" s="47"/>
+      <c r="O15" s="85"/>
       <c r="Q15" s="47"/>
       <c r="R15" s="47"/>
       <c r="S15" s="47"/>
       <c r="T15" s="47"/>
       <c r="U15" s="47"/>
       <c r="V15" s="47"/>
-      <c r="AC15" s="47"/>
+      <c r="W15" s="47"/>
       <c r="AD15" s="47"/>
       <c r="AE15" s="47"/>
       <c r="AF15" s="47"/>
       <c r="AG15" s="47"/>
-    </row>
-    <row r="16" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH15" s="47"/>
+    </row>
+    <row r="16" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B16" s="126"/>
       <c r="C16" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="94" t="s">
+      <c r="D16" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="95"/>
-      <c r="F16" s="83" t="s">
+      <c r="F16" s="95"/>
+      <c r="G16" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="85" t="s">
+      <c r="H16" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H16" s="174">
+      <c r="I16" s="174">
         <v>6</v>
       </c>
-      <c r="I16" s="174" t="s">
+      <c r="J16" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="165"/>
-      <c r="K16" s="141">
+      <c r="K16" s="165"/>
+      <c r="L16" s="141">
         <v>663</v>
       </c>
-      <c r="L16" s="121">
+      <c r="M16" s="121">
         <v>698.5</v>
       </c>
-      <c r="M16" s="121">
+      <c r="N16" s="121">
         <v>4191</v>
       </c>
-      <c r="N16" s="85"/>
-      <c r="P16" s="47"/>
+      <c r="O16" s="85"/>
       <c r="Q16" s="47"/>
       <c r="R16" s="47"/>
       <c r="S16" s="47"/>
       <c r="T16" s="47"/>
       <c r="U16" s="47"/>
       <c r="V16" s="47"/>
-      <c r="AC16" s="47"/>
+      <c r="W16" s="47"/>
       <c r="AD16" s="47"/>
       <c r="AE16" s="47"/>
       <c r="AF16" s="47"/>
       <c r="AG16" s="47"/>
-    </row>
-    <row r="17" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH16" s="47"/>
+    </row>
+    <row r="17" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B17" s="126"/>
       <c r="C17" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="94" t="s">
+      <c r="D17" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="95"/>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="95"/>
+      <c r="G17" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="85" t="s">
+      <c r="H17" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H17" s="174">
+      <c r="I17" s="174">
         <v>6</v>
       </c>
-      <c r="I17" s="174" t="s">
+      <c r="J17" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="165"/>
-      <c r="K17" s="141">
+      <c r="K17" s="165"/>
+      <c r="L17" s="141">
         <v>7.2</v>
       </c>
-      <c r="L17" s="121">
+      <c r="M17" s="121">
         <v>7.5</v>
       </c>
-      <c r="M17" s="121">
+      <c r="N17" s="121">
         <v>45</v>
       </c>
-      <c r="N17" s="85"/>
-      <c r="P17" s="47"/>
+      <c r="O17" s="85"/>
       <c r="Q17" s="47"/>
       <c r="R17" s="47"/>
       <c r="S17" s="47"/>
       <c r="T17" s="47"/>
       <c r="U17" s="47"/>
       <c r="V17" s="47"/>
-      <c r="AC17" s="47"/>
+      <c r="W17" s="47"/>
       <c r="AD17" s="47"/>
       <c r="AE17" s="47"/>
       <c r="AF17" s="47"/>
       <c r="AG17" s="47"/>
-    </row>
-    <row r="18" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH17" s="47"/>
+    </row>
+    <row r="18" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B18" s="129">
         <v>2</v>
       </c>
       <c r="C18" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="172"/>
-      <c r="F18" s="175" t="s">
+      <c r="F18" s="172"/>
+      <c r="G18" s="175" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="176" t="s">
+      <c r="H18" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="H18" s="177">
+      <c r="I18" s="177">
         <v>1</v>
       </c>
-      <c r="I18" s="177" t="s">
+      <c r="J18" s="177" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="178" t="s">
+      <c r="K18" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="163">
+      <c r="L18" s="163">
         <v>1568</v>
       </c>
-      <c r="L18" s="154"/>
-      <c r="M18" s="154">
+      <c r="M18" s="154"/>
+      <c r="N18" s="154">
         <v>9817.5</v>
       </c>
-      <c r="N18" s="176" t="s">
+      <c r="O18" s="176" t="s">
         <v>37</v>
       </c>
-      <c r="P18" s="47"/>
       <c r="Q18" s="47"/>
       <c r="R18" s="47"/>
       <c r="S18" s="47"/>
       <c r="T18" s="47"/>
       <c r="U18" s="47"/>
       <c r="V18" s="47"/>
-      <c r="AC18" s="47"/>
+      <c r="W18" s="47"/>
       <c r="AD18" s="47"/>
       <c r="AE18" s="47"/>
       <c r="AF18" s="47"/>
       <c r="AG18" s="47"/>
-    </row>
-    <row r="19" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH18" s="47"/>
+    </row>
+    <row r="19" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B19" s="129"/>
       <c r="C19" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="161" t="s">
+      <c r="D19" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="161" t="s">
         <v>216</v>
       </c>
-      <c r="E19" s="172"/>
-      <c r="F19" s="83" t="s">
+      <c r="F19" s="172"/>
+      <c r="G19" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="165" t="s">
+      <c r="H19" s="165" t="s">
         <v>203</v>
       </c>
-      <c r="H19" s="174">
+      <c r="I19" s="174">
         <v>40</v>
       </c>
-      <c r="I19" s="174" t="s">
+      <c r="J19" s="174" t="s">
         <v>214</v>
       </c>
-      <c r="J19" s="179"/>
-      <c r="K19" s="155">
+      <c r="K19" s="179"/>
+      <c r="L19" s="155">
         <v>1068</v>
       </c>
-      <c r="L19" s="156">
+      <c r="M19" s="156">
         <v>149.28000000000003</v>
       </c>
-      <c r="M19" s="156">
+      <c r="N19" s="156">
         <v>5971.2000000000007</v>
       </c>
-      <c r="N19" s="176"/>
-      <c r="P19" s="47"/>
+      <c r="O19" s="176"/>
       <c r="Q19" s="47"/>
       <c r="R19" s="47"/>
       <c r="S19" s="47"/>
       <c r="T19" s="47"/>
       <c r="U19" s="47"/>
       <c r="V19" s="47"/>
-      <c r="AC19" s="47"/>
+      <c r="W19" s="47"/>
       <c r="AD19" s="47"/>
       <c r="AE19" s="47"/>
       <c r="AF19" s="47"/>
       <c r="AG19" s="47"/>
-    </row>
-    <row r="20" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH19" s="47"/>
+    </row>
+    <row r="20" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B20" s="129"/>
       <c r="C20" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="161" t="s">
+      <c r="D20" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" s="161" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="172"/>
-      <c r="F20" s="83" t="s">
+      <c r="F20" s="172"/>
+      <c r="G20" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="165" t="s">
+      <c r="H20" s="165" t="s">
         <v>203</v>
       </c>
-      <c r="H20" s="11">
+      <c r="I20" s="11">
         <v>160</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="J20" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="J20" s="179"/>
-      <c r="K20" s="155">
+      <c r="K20" s="179"/>
+      <c r="L20" s="155">
         <v>280</v>
       </c>
-      <c r="L20" s="156">
+      <c r="M20" s="156">
         <v>15.4375</v>
       </c>
-      <c r="M20" s="156">
+      <c r="N20" s="156">
         <v>2470</v>
       </c>
-      <c r="N20" s="176"/>
-      <c r="P20" s="47"/>
+      <c r="O20" s="176"/>
       <c r="Q20" s="47"/>
       <c r="R20" s="47"/>
       <c r="S20" s="47"/>
       <c r="T20" s="47"/>
       <c r="U20" s="47"/>
       <c r="V20" s="47"/>
-      <c r="AC20" s="47"/>
+      <c r="W20" s="47"/>
       <c r="AD20" s="47"/>
       <c r="AE20" s="47"/>
       <c r="AF20" s="47"/>
       <c r="AG20" s="47"/>
-    </row>
-    <row r="21" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH20" s="47"/>
+    </row>
+    <row r="21" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B21" s="126"/>
       <c r="C21" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="161" t="s">
+      <c r="D21" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="161" t="s">
         <v>216</v>
       </c>
-      <c r="E21" s="168"/>
-      <c r="F21" s="83" t="s">
+      <c r="F21" s="168"/>
+      <c r="G21" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="85" t="s">
+      <c r="H21" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H21" s="81">
+      <c r="I21" s="81">
         <v>16</v>
       </c>
-      <c r="I21" s="81" t="s">
+      <c r="J21" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="J21" s="85"/>
-      <c r="K21" s="155">
+      <c r="K21" s="85"/>
+      <c r="L21" s="155">
         <v>181.6</v>
       </c>
-      <c r="L21" s="156">
+      <c r="M21" s="156">
         <v>66.018749999999997</v>
       </c>
-      <c r="M21" s="156">
+      <c r="N21" s="156">
         <v>1056.3</v>
       </c>
-      <c r="N21" s="85"/>
-      <c r="P21" s="47"/>
+      <c r="O21" s="85"/>
       <c r="Q21" s="47"/>
       <c r="R21" s="47"/>
       <c r="S21" s="47"/>
       <c r="T21" s="47"/>
       <c r="U21" s="47"/>
       <c r="V21" s="47"/>
-      <c r="AC21" s="47"/>
+      <c r="W21" s="47"/>
       <c r="AD21" s="47"/>
       <c r="AE21" s="47"/>
       <c r="AF21" s="47"/>
       <c r="AG21" s="47"/>
-    </row>
-    <row r="22" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH21" s="47"/>
+    </row>
+    <row r="22" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B22" s="126"/>
       <c r="C22" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="161" t="s">
+      <c r="D22" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" s="161" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="168"/>
-      <c r="F22" s="83" t="s">
+      <c r="F22" s="168"/>
+      <c r="G22" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="85" t="s">
+      <c r="H22" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H22" s="164">
+      <c r="I22" s="164">
         <v>64</v>
       </c>
-      <c r="I22" s="81" t="s">
+      <c r="J22" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="J22" s="85"/>
-      <c r="K22" s="155">
+      <c r="K22" s="85"/>
+      <c r="L22" s="155">
         <v>38.4</v>
       </c>
-      <c r="L22" s="156">
+      <c r="M22" s="156">
         <v>5</v>
       </c>
-      <c r="M22" s="156">
+      <c r="N22" s="156">
         <v>320</v>
       </c>
-      <c r="N22" s="85"/>
-      <c r="P22" s="47"/>
+      <c r="O22" s="85"/>
       <c r="Q22" s="47"/>
       <c r="R22" s="47"/>
       <c r="S22" s="47"/>
       <c r="T22" s="47"/>
       <c r="U22" s="47"/>
       <c r="V22" s="47"/>
-      <c r="AC22" s="47"/>
+      <c r="W22" s="47"/>
       <c r="AD22" s="47"/>
       <c r="AE22" s="47"/>
       <c r="AF22" s="47"/>
       <c r="AG22" s="47"/>
-    </row>
-    <row r="23" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH22" s="47"/>
+    </row>
+    <row r="23" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B23" s="129">
         <v>3</v>
       </c>
       <c r="C23" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="130" t="s">
+      <c r="D23" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E23" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="172"/>
-      <c r="F23" s="175" t="s">
+      <c r="F23" s="172"/>
+      <c r="G23" s="175" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="176" t="s">
+      <c r="H23" s="176" t="s">
         <v>203</v>
       </c>
-      <c r="H23" s="177">
+      <c r="I23" s="177">
         <v>1</v>
       </c>
-      <c r="I23" s="177" t="s">
+      <c r="J23" s="177" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="178" t="s">
+      <c r="K23" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="163">
+      <c r="L23" s="163">
         <v>2120</v>
       </c>
-      <c r="L23" s="154"/>
-      <c r="M23" s="154">
+      <c r="M23" s="154"/>
+      <c r="N23" s="154">
         <v>13008.1875</v>
       </c>
-      <c r="N23" s="176" t="s">
+      <c r="O23" s="176" t="s">
         <v>37</v>
       </c>
-      <c r="P23" s="47"/>
       <c r="Q23" s="47"/>
       <c r="R23" s="47"/>
       <c r="S23" s="47"/>
       <c r="T23" s="47"/>
       <c r="U23" s="47"/>
       <c r="V23" s="47"/>
-      <c r="AC23" s="47"/>
+      <c r="W23" s="47"/>
       <c r="AD23" s="47"/>
       <c r="AE23" s="47"/>
       <c r="AF23" s="47"/>
       <c r="AG23" s="47"/>
-    </row>
-    <row r="24" spans="1:33" s="48" customFormat="1" ht="28.15" customHeight="1">
+      <c r="AH23" s="47"/>
+    </row>
+    <row r="24" spans="1:34" s="48" customFormat="1" ht="28.15" customHeight="1">
       <c r="B24" s="126"/>
       <c r="C24" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="161" t="s">
+      <c r="D24" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="161" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="168"/>
-      <c r="F24" s="83" t="s">
+      <c r="F24" s="168"/>
+      <c r="G24" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="165" t="s">
+      <c r="H24" s="165" t="s">
         <v>203</v>
       </c>
-      <c r="H24" s="174">
+      <c r="I24" s="174">
         <v>53</v>
       </c>
-      <c r="I24" s="174" t="s">
+      <c r="J24" s="174" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="165"/>
-      <c r="K24" s="155">
-        <f>K23-K25</f>
+      <c r="K24" s="165"/>
+      <c r="L24" s="155">
+        <f>L23-L25</f>
         <v>1707.78</v>
       </c>
-      <c r="L24" s="156">
+      <c r="M24" s="156">
         <v>169.6875</v>
       </c>
-      <c r="M24" s="156">
-        <f>M23-M25</f>
+      <c r="N24" s="156">
+        <f>N23-N25</f>
         <v>8993.4375</v>
       </c>
-      <c r="N24" s="165"/>
-      <c r="P24" s="47"/>
+      <c r="O24" s="165"/>
       <c r="Q24" s="47"/>
       <c r="R24" s="47"/>
       <c r="S24" s="47"/>
       <c r="T24" s="47"/>
       <c r="U24" s="47"/>
       <c r="V24" s="47"/>
-      <c r="AC24" s="47"/>
+      <c r="W24" s="47"/>
       <c r="AD24" s="47"/>
       <c r="AE24" s="47"/>
       <c r="AF24" s="47"/>
       <c r="AG24" s="47"/>
-    </row>
-    <row r="25" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH24" s="47"/>
+    </row>
+    <row r="25" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B25" s="126"/>
       <c r="C25" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="161" t="s">
+      <c r="D25" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="161" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="168"/>
-      <c r="F25" s="83" t="s">
+      <c r="F25" s="168"/>
+      <c r="G25" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="85" t="s">
+      <c r="H25" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H25" s="164">
+      <c r="I25" s="164">
         <v>212</v>
       </c>
-      <c r="I25" s="81" t="s">
+      <c r="J25" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="86"/>
-      <c r="K25" s="155">
+      <c r="K25" s="86"/>
+      <c r="L25" s="155">
         <v>412.22</v>
       </c>
-      <c r="L25" s="156">
+      <c r="M25" s="156">
         <v>18.9375</v>
       </c>
-      <c r="M25" s="156">
-        <f>L25*H25</f>
+      <c r="N25" s="156">
+        <f>M25*I25</f>
         <v>4014.75</v>
       </c>
-      <c r="N25" s="85"/>
-      <c r="P25" s="47"/>
+      <c r="O25" s="85"/>
       <c r="Q25" s="47"/>
       <c r="R25" s="47"/>
       <c r="S25" s="47"/>
       <c r="T25" s="47"/>
       <c r="U25" s="47"/>
       <c r="V25" s="47"/>
-      <c r="AC25" s="47"/>
+      <c r="W25" s="47"/>
       <c r="AD25" s="47"/>
       <c r="AE25" s="47"/>
       <c r="AF25" s="47"/>
       <c r="AG25" s="47"/>
-    </row>
-    <row r="26" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH25" s="47"/>
+    </row>
+    <row r="26" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B26" s="129">
         <v>4</v>
       </c>
       <c r="C26" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="130" t="s">
+      <c r="D26" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="172"/>
-      <c r="F26" s="129" t="s">
+      <c r="F26" s="172"/>
+      <c r="G26" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="132" t="s">
+      <c r="H26" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H26" s="173">
+      <c r="I26" s="173">
         <v>1</v>
       </c>
-      <c r="I26" s="133" t="s">
+      <c r="J26" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="134" t="s">
+      <c r="K26" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="163">
+      <c r="L26" s="163">
         <v>2120</v>
       </c>
-      <c r="L26" s="154"/>
-      <c r="M26" s="154">
+      <c r="M26" s="154"/>
+      <c r="N26" s="154">
         <v>13008.1875</v>
       </c>
-      <c r="N26" s="132" t="s">
+      <c r="O26" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="P26" s="47"/>
       <c r="Q26" s="47"/>
       <c r="R26" s="47"/>
       <c r="S26" s="47"/>
       <c r="T26" s="47"/>
       <c r="U26" s="47"/>
       <c r="V26" s="47"/>
-      <c r="AC26" s="47"/>
+      <c r="W26" s="47"/>
       <c r="AD26" s="47"/>
       <c r="AE26" s="47"/>
       <c r="AF26" s="47"/>
       <c r="AG26" s="47"/>
-    </row>
-    <row r="27" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH26" s="47"/>
+    </row>
+    <row r="27" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B27" s="129"/>
       <c r="C27" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="161" t="s">
+      <c r="D27" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="161" t="s">
         <v>215</v>
       </c>
-      <c r="E27" s="172"/>
-      <c r="F27" s="83" t="s">
+      <c r="F27" s="172"/>
+      <c r="G27" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G27" s="165" t="s">
+      <c r="H27" s="165" t="s">
         <v>203</v>
       </c>
-      <c r="H27" s="174">
+      <c r="I27" s="174">
         <v>53</v>
       </c>
-      <c r="I27" s="174" t="s">
+      <c r="J27" s="174" t="s">
         <v>214</v>
       </c>
-      <c r="J27" s="134"/>
-      <c r="K27" s="155">
+      <c r="K27" s="134"/>
+      <c r="L27" s="155">
         <v>1707.78</v>
       </c>
-      <c r="L27" s="156">
+      <c r="M27" s="156">
         <v>169.6875</v>
       </c>
-      <c r="M27" s="156">
+      <c r="N27" s="156">
         <v>8993.4375</v>
       </c>
-      <c r="N27" s="132"/>
-      <c r="P27" s="47"/>
+      <c r="O27" s="132"/>
       <c r="Q27" s="47"/>
       <c r="R27" s="47"/>
       <c r="S27" s="47"/>
       <c r="T27" s="47"/>
       <c r="U27" s="47"/>
       <c r="V27" s="47"/>
-      <c r="AC27" s="47"/>
+      <c r="W27" s="47"/>
       <c r="AD27" s="47"/>
       <c r="AE27" s="47"/>
       <c r="AF27" s="47"/>
       <c r="AG27" s="47"/>
-    </row>
-    <row r="28" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH27" s="47"/>
+    </row>
+    <row r="28" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B28" s="126"/>
       <c r="C28" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="161" t="s">
+      <c r="D28" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" s="161" t="s">
         <v>161</v>
       </c>
-      <c r="E28" s="168"/>
-      <c r="F28" s="83" t="s">
+      <c r="F28" s="168"/>
+      <c r="G28" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="85" t="s">
+      <c r="H28" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H28" s="164">
+      <c r="I28" s="164">
         <v>212</v>
       </c>
-      <c r="I28" s="81" t="s">
+      <c r="J28" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="J28" s="86"/>
-      <c r="K28" s="155">
+      <c r="K28" s="86"/>
+      <c r="L28" s="155">
         <v>412.22</v>
       </c>
-      <c r="L28" s="156">
+      <c r="M28" s="156">
         <v>18.9375</v>
       </c>
-      <c r="M28" s="156">
+      <c r="N28" s="156">
         <v>4014.75</v>
       </c>
-      <c r="N28" s="85"/>
-      <c r="P28" s="47"/>
+      <c r="O28" s="85"/>
       <c r="Q28" s="47"/>
       <c r="R28" s="47"/>
       <c r="S28" s="47"/>
       <c r="T28" s="47"/>
       <c r="U28" s="47"/>
       <c r="V28" s="47"/>
-      <c r="AC28" s="47"/>
+      <c r="W28" s="47"/>
       <c r="AD28" s="47"/>
       <c r="AE28" s="47"/>
       <c r="AF28" s="47"/>
       <c r="AG28" s="47"/>
-    </row>
-    <row r="29" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH28" s="47"/>
+    </row>
+    <row r="29" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="A29" s="48" t="s">
         <v>40</v>
       </c>
@@ -4863,1609 +4865,1713 @@
       <c r="C29" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="130" t="s">
+      <c r="D29" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="172"/>
-      <c r="F29" s="129" t="s">
+      <c r="F29" s="172"/>
+      <c r="G29" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="G29" s="132" t="s">
+      <c r="H29" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H29" s="173">
+      <c r="I29" s="173">
         <v>1</v>
       </c>
-      <c r="I29" s="133" t="s">
+      <c r="J29" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="134" t="s">
+      <c r="K29" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K29" s="163">
+      <c r="L29" s="163">
         <v>2160</v>
       </c>
-      <c r="L29" s="154"/>
-      <c r="M29" s="154">
+      <c r="M29" s="154"/>
+      <c r="N29" s="154">
         <v>13253.625</v>
       </c>
-      <c r="N29" s="132" t="s">
+      <c r="O29" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="P29" s="47"/>
       <c r="Q29" s="47"/>
       <c r="R29" s="47"/>
       <c r="S29" s="47"/>
       <c r="T29" s="47"/>
       <c r="U29" s="47"/>
       <c r="V29" s="47"/>
-      <c r="AC29" s="47"/>
+      <c r="W29" s="47"/>
       <c r="AD29" s="47"/>
       <c r="AE29" s="47"/>
       <c r="AF29" s="47"/>
       <c r="AG29" s="47"/>
-    </row>
-    <row r="30" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH29" s="47"/>
+    </row>
+    <row r="30" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B30" s="129"/>
       <c r="C30" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="161" t="s">
+      <c r="D30" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="161" t="s">
         <v>215</v>
       </c>
-      <c r="E30" s="172"/>
-      <c r="F30" s="83" t="s">
+      <c r="F30" s="172"/>
+      <c r="G30" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="165" t="s">
+      <c r="H30" s="165" t="s">
         <v>203</v>
       </c>
-      <c r="H30" s="174">
+      <c r="I30" s="174">
         <v>54</v>
       </c>
-      <c r="I30" s="174" t="s">
+      <c r="J30" s="174" t="s">
         <v>214</v>
       </c>
-      <c r="J30" s="134"/>
-      <c r="K30" s="155">
-        <f>K29-K31</f>
+      <c r="K30" s="134"/>
+      <c r="L30" s="155">
+        <f>L29-L31</f>
         <v>1944</v>
       </c>
-      <c r="L30" s="156">
+      <c r="M30" s="156">
         <v>169.6875</v>
       </c>
-      <c r="M30" s="156">
+      <c r="N30" s="156">
         <v>9163.125</v>
       </c>
-      <c r="N30" s="132"/>
-      <c r="P30" s="47"/>
+      <c r="O30" s="132"/>
       <c r="Q30" s="47"/>
       <c r="R30" s="47"/>
       <c r="S30" s="47"/>
       <c r="T30" s="47"/>
       <c r="U30" s="47"/>
       <c r="V30" s="47"/>
-      <c r="AC30" s="47"/>
+      <c r="W30" s="47"/>
       <c r="AD30" s="47"/>
       <c r="AE30" s="47"/>
       <c r="AF30" s="47"/>
       <c r="AG30" s="47"/>
-    </row>
-    <row r="31" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH30" s="47"/>
+    </row>
+    <row r="31" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B31" s="126"/>
       <c r="C31" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="161" t="s">
+      <c r="D31" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="161" t="s">
         <v>161</v>
       </c>
-      <c r="E31" s="168"/>
-      <c r="F31" s="83" t="s">
+      <c r="F31" s="168"/>
+      <c r="G31" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="85" t="s">
+      <c r="H31" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H31" s="164">
+      <c r="I31" s="164">
         <v>216</v>
       </c>
-      <c r="I31" s="174" t="s">
+      <c r="J31" s="174" t="s">
         <v>214</v>
       </c>
-      <c r="J31" s="86"/>
-      <c r="K31" s="155">
+      <c r="K31" s="86"/>
+      <c r="L31" s="155">
         <v>216</v>
       </c>
-      <c r="L31" s="156">
+      <c r="M31" s="156">
         <v>18.9375</v>
       </c>
-      <c r="M31" s="156">
+      <c r="N31" s="156">
         <v>4090.5</v>
       </c>
-      <c r="N31" s="85"/>
-      <c r="P31" s="47"/>
+      <c r="O31" s="85"/>
       <c r="Q31" s="47"/>
       <c r="R31" s="47"/>
       <c r="S31" s="47"/>
       <c r="T31" s="47"/>
       <c r="U31" s="47"/>
       <c r="V31" s="47"/>
-      <c r="AC31" s="47"/>
+      <c r="W31" s="47"/>
       <c r="AD31" s="47"/>
       <c r="AE31" s="47"/>
       <c r="AF31" s="47"/>
       <c r="AG31" s="47"/>
-    </row>
-    <row r="32" spans="1:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH31" s="47"/>
+    </row>
+    <row r="32" spans="1:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B32" s="129">
         <v>6</v>
       </c>
       <c r="C32" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="130" t="s">
+      <c r="D32" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="172"/>
-      <c r="F32" s="129" t="s">
+      <c r="F32" s="172"/>
+      <c r="G32" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="132" t="s">
+      <c r="H32" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H32" s="173">
+      <c r="I32" s="173">
         <v>1</v>
       </c>
-      <c r="I32" s="133" t="s">
+      <c r="J32" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="134" t="s">
+      <c r="K32" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K32" s="163">
+      <c r="L32" s="163">
         <v>2376</v>
       </c>
-      <c r="L32" s="154"/>
-      <c r="M32" s="154">
+      <c r="M32" s="154"/>
+      <c r="N32" s="154">
         <v>14279.999999999976</v>
       </c>
-      <c r="N32" s="132" t="s">
+      <c r="O32" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="P32" s="47"/>
       <c r="Q32" s="47"/>
       <c r="R32" s="47"/>
       <c r="S32" s="47"/>
       <c r="T32" s="47"/>
       <c r="U32" s="47"/>
       <c r="V32" s="47"/>
-      <c r="AC32" s="47"/>
+      <c r="W32" s="47"/>
       <c r="AD32" s="47"/>
       <c r="AE32" s="47"/>
       <c r="AF32" s="47"/>
       <c r="AG32" s="47"/>
-    </row>
-    <row r="33" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH32" s="47"/>
+    </row>
+    <row r="33" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B33" s="129"/>
       <c r="C33" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="161" t="s">
+      <c r="D33" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" s="161" t="s">
         <v>215</v>
       </c>
-      <c r="E33" s="172"/>
-      <c r="F33" s="83" t="s">
+      <c r="F33" s="172"/>
+      <c r="G33" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G33" s="165" t="s">
+      <c r="H33" s="165" t="s">
         <v>203</v>
       </c>
-      <c r="H33" s="174">
+      <c r="I33" s="174">
         <v>72</v>
       </c>
-      <c r="I33" s="174" t="s">
+      <c r="J33" s="174" t="s">
         <v>214</v>
       </c>
-      <c r="J33" s="134"/>
-      <c r="K33" s="155">
+      <c r="K33" s="134"/>
+      <c r="L33" s="155">
         <v>2046.8571428571429</v>
       </c>
-      <c r="L33" s="156">
+      <c r="M33" s="156">
         <v>158.90476190476159</v>
       </c>
-      <c r="M33" s="156">
+      <c r="N33" s="156">
         <v>11441.142857142833</v>
       </c>
-      <c r="N33" s="132"/>
-      <c r="P33" s="47"/>
+      <c r="O33" s="132"/>
       <c r="Q33" s="47"/>
       <c r="R33" s="47"/>
       <c r="S33" s="47"/>
       <c r="T33" s="47"/>
       <c r="U33" s="47"/>
       <c r="V33" s="47"/>
-      <c r="AC33" s="47"/>
+      <c r="W33" s="47"/>
       <c r="AD33" s="47"/>
       <c r="AE33" s="47"/>
       <c r="AF33" s="47"/>
       <c r="AG33" s="47"/>
-    </row>
-    <row r="34" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH33" s="47"/>
+    </row>
+    <row r="34" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B34" s="126"/>
       <c r="C34" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="161" t="s">
+      <c r="D34" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" s="161" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="168"/>
-      <c r="F34" s="83" t="s">
+      <c r="F34" s="168"/>
+      <c r="G34" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G34" s="85" t="s">
+      <c r="H34" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H34" s="81">
+      <c r="I34" s="81">
         <v>288</v>
       </c>
-      <c r="I34" s="81" t="s">
+      <c r="J34" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="J34" s="86"/>
-      <c r="K34" s="155">
+      <c r="K34" s="86"/>
+      <c r="L34" s="155">
         <v>329.14285714285711</v>
       </c>
-      <c r="L34" s="156">
+      <c r="M34" s="156">
         <v>9.8571428571428577</v>
       </c>
-      <c r="M34" s="156">
+      <c r="N34" s="156">
         <v>2838.8571428571431</v>
       </c>
-      <c r="N34" s="85"/>
-      <c r="P34" s="47"/>
+      <c r="O34" s="85"/>
       <c r="Q34" s="47"/>
       <c r="R34" s="47"/>
       <c r="S34" s="47"/>
       <c r="T34" s="47"/>
       <c r="U34" s="47"/>
       <c r="V34" s="47"/>
-      <c r="AC34" s="47"/>
+      <c r="W34" s="47"/>
       <c r="AD34" s="47"/>
       <c r="AE34" s="47"/>
       <c r="AF34" s="47"/>
       <c r="AG34" s="47"/>
-    </row>
-    <row r="35" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH34" s="47"/>
+    </row>
+    <row r="35" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B35" s="129">
         <v>7</v>
       </c>
       <c r="C35" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="130" t="s">
+      <c r="D35" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E35" s="131"/>
-      <c r="F35" s="129" t="s">
+      <c r="F35" s="131"/>
+      <c r="G35" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="G35" s="132" t="s">
+      <c r="H35" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H35" s="133">
+      <c r="I35" s="133">
         <v>1</v>
       </c>
-      <c r="I35" s="133" t="s">
+      <c r="J35" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="134" t="s">
+      <c r="K35" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="140">
+      <c r="L35" s="140">
         <v>1567</v>
       </c>
-      <c r="L35" s="135"/>
-      <c r="M35" s="135">
+      <c r="M35" s="135"/>
+      <c r="N35" s="135">
         <v>9496.5</v>
       </c>
-      <c r="N35" s="132" t="s">
+      <c r="O35" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="P35" s="47"/>
       <c r="Q35" s="47"/>
       <c r="R35" s="47"/>
       <c r="S35" s="47"/>
       <c r="T35" s="47"/>
       <c r="U35" s="47"/>
       <c r="V35" s="47"/>
-      <c r="AC35" s="47"/>
+      <c r="W35" s="47"/>
       <c r="AD35" s="47"/>
       <c r="AE35" s="47"/>
       <c r="AF35" s="47"/>
       <c r="AG35" s="47"/>
-    </row>
-    <row r="36" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH35" s="47"/>
+    </row>
+    <row r="36" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B36" s="126"/>
       <c r="C36" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="94" t="s">
+      <c r="D36" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="95"/>
-      <c r="F36" s="83" t="s">
+      <c r="F36" s="95"/>
+      <c r="G36" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="85" t="s">
+      <c r="H36" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H36" s="81">
+      <c r="I36" s="81">
         <v>40</v>
       </c>
-      <c r="I36" s="81" t="s">
+      <c r="J36" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J36" s="101"/>
-      <c r="K36" s="141">
+      <c r="K36" s="101"/>
+      <c r="L36" s="141">
         <v>132</v>
       </c>
-      <c r="L36" s="121">
+      <c r="M36" s="121">
         <v>20</v>
       </c>
-      <c r="M36" s="121">
+      <c r="N36" s="121">
         <v>800</v>
       </c>
-      <c r="N36" s="85"/>
-      <c r="P36" s="47"/>
+      <c r="O36" s="85"/>
       <c r="Q36" s="47"/>
       <c r="R36" s="47"/>
       <c r="S36" s="47"/>
       <c r="T36" s="47"/>
       <c r="U36" s="47"/>
       <c r="V36" s="47"/>
-      <c r="AC36" s="47"/>
+      <c r="W36" s="47"/>
       <c r="AD36" s="47"/>
       <c r="AE36" s="47"/>
       <c r="AF36" s="47"/>
       <c r="AG36" s="47"/>
-    </row>
-    <row r="37" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH36" s="47"/>
+    </row>
+    <row r="37" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B37" s="126"/>
       <c r="C37" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="94" t="s">
+      <c r="D37" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E37" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="95"/>
-      <c r="F37" s="83" t="s">
+      <c r="F37" s="95"/>
+      <c r="G37" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G37" s="85" t="s">
+      <c r="H37" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H37" s="81">
+      <c r="I37" s="81">
         <v>160</v>
       </c>
-      <c r="I37" s="81" t="s">
+      <c r="J37" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J37" s="85"/>
-      <c r="K37" s="141">
+      <c r="K37" s="85"/>
+      <c r="L37" s="141">
         <v>432</v>
       </c>
-      <c r="L37" s="121">
+      <c r="M37" s="121">
         <v>16.345238095238095</v>
       </c>
-      <c r="M37" s="121">
+      <c r="N37" s="121">
         <v>2615.2380952380954</v>
       </c>
-      <c r="N37" s="85"/>
-      <c r="P37" s="47"/>
+      <c r="O37" s="85"/>
       <c r="Q37" s="47"/>
       <c r="R37" s="47"/>
       <c r="S37" s="47"/>
       <c r="T37" s="47"/>
       <c r="U37" s="47"/>
       <c r="V37" s="47"/>
-      <c r="AC37" s="47"/>
+      <c r="W37" s="47"/>
       <c r="AD37" s="47"/>
       <c r="AE37" s="47"/>
       <c r="AF37" s="47"/>
       <c r="AG37" s="47"/>
-    </row>
-    <row r="38" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH37" s="47"/>
+    </row>
+    <row r="38" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B38" s="126"/>
       <c r="C38" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="94" t="s">
+      <c r="D38" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="95"/>
-      <c r="F38" s="83" t="s">
+      <c r="F38" s="95"/>
+      <c r="G38" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G38" s="85" t="s">
+      <c r="H38" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H38" s="81">
+      <c r="I38" s="81">
         <v>16</v>
       </c>
-      <c r="I38" s="81" t="s">
+      <c r="J38" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J38" s="85"/>
-      <c r="K38" s="141">
+      <c r="K38" s="85"/>
+      <c r="L38" s="141">
         <v>19</v>
       </c>
-      <c r="L38" s="121">
+      <c r="M38" s="121">
         <v>7.1904761904761907</v>
       </c>
-      <c r="M38" s="121">
+      <c r="N38" s="121">
         <v>115.04761904761905</v>
       </c>
-      <c r="N38" s="85"/>
-      <c r="P38" s="47"/>
+      <c r="O38" s="85"/>
       <c r="Q38" s="47"/>
       <c r="R38" s="47"/>
       <c r="S38" s="47"/>
       <c r="T38" s="47"/>
       <c r="U38" s="47"/>
       <c r="V38" s="47"/>
-      <c r="AC38" s="47"/>
+      <c r="W38" s="47"/>
       <c r="AD38" s="47"/>
       <c r="AE38" s="47"/>
       <c r="AF38" s="47"/>
       <c r="AG38" s="47"/>
-    </row>
-    <row r="39" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH38" s="47"/>
+    </row>
+    <row r="39" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B39" s="126"/>
       <c r="C39" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="96" t="s">
+      <c r="D39" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E39" s="95"/>
-      <c r="F39" s="83" t="s">
+      <c r="F39" s="95"/>
+      <c r="G39" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="85" t="s">
+      <c r="H39" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H39" s="81">
+      <c r="I39" s="81">
         <v>72</v>
       </c>
-      <c r="I39" s="81" t="s">
+      <c r="J39" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="85"/>
-      <c r="K39" s="142">
+      <c r="K39" s="85"/>
+      <c r="L39" s="142">
         <v>129</v>
       </c>
-      <c r="L39" s="121">
+      <c r="M39" s="121">
         <v>10.857142857142858</v>
       </c>
-      <c r="M39" s="121">
+      <c r="N39" s="121">
         <v>781.71428571428578</v>
       </c>
-      <c r="N39" s="85"/>
-      <c r="P39" s="47"/>
+      <c r="O39" s="85"/>
       <c r="Q39" s="47"/>
       <c r="R39" s="47"/>
       <c r="S39" s="47"/>
       <c r="T39" s="47"/>
       <c r="U39" s="47"/>
       <c r="V39" s="47"/>
-      <c r="AC39" s="47"/>
+      <c r="W39" s="47"/>
       <c r="AD39" s="47"/>
       <c r="AE39" s="47"/>
       <c r="AF39" s="47"/>
       <c r="AG39" s="47"/>
-    </row>
-    <row r="40" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH39" s="47"/>
+    </row>
+    <row r="40" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B40" s="126"/>
       <c r="C40" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="94" t="s">
+      <c r="D40" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="95"/>
-      <c r="F40" s="83" t="s">
+      <c r="F40" s="95"/>
+      <c r="G40" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="85" t="s">
+      <c r="H40" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H40" s="81">
+      <c r="I40" s="81">
         <v>40</v>
       </c>
-      <c r="I40" s="81" t="s">
+      <c r="J40" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J40" s="85"/>
-      <c r="K40" s="142">
+      <c r="K40" s="85"/>
+      <c r="L40" s="142">
         <v>108</v>
       </c>
-      <c r="L40" s="121">
+      <c r="M40" s="121">
         <v>16.37</v>
       </c>
-      <c r="M40" s="121">
+      <c r="N40" s="121">
         <v>654.80000000000007</v>
       </c>
-      <c r="N40" s="85"/>
-      <c r="P40" s="47"/>
+      <c r="O40" s="85"/>
       <c r="Q40" s="47"/>
       <c r="R40" s="47"/>
       <c r="S40" s="47"/>
       <c r="T40" s="47"/>
       <c r="U40" s="47"/>
       <c r="V40" s="47"/>
-      <c r="AC40" s="47"/>
+      <c r="W40" s="47"/>
       <c r="AD40" s="47"/>
       <c r="AE40" s="47"/>
       <c r="AF40" s="47"/>
       <c r="AG40" s="47"/>
-    </row>
-    <row r="41" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH40" s="47"/>
+    </row>
+    <row r="41" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B41" s="126"/>
       <c r="C41" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="94" t="s">
+      <c r="D41" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E41" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="95"/>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="95"/>
+      <c r="G41" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="85" t="s">
+      <c r="H41" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H41" s="81">
+      <c r="I41" s="81">
         <v>160</v>
       </c>
-      <c r="I41" s="81" t="s">
+      <c r="J41" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="85"/>
-      <c r="K41" s="142">
+      <c r="K41" s="85"/>
+      <c r="L41" s="142">
         <v>432</v>
       </c>
-      <c r="L41" s="121">
+      <c r="M41" s="121">
         <v>16.37</v>
       </c>
-      <c r="M41" s="121">
+      <c r="N41" s="121">
         <v>2619.2000000000003</v>
       </c>
-      <c r="N41" s="85"/>
-      <c r="P41" s="47"/>
+      <c r="O41" s="85"/>
       <c r="Q41" s="47"/>
       <c r="R41" s="47"/>
       <c r="S41" s="47"/>
       <c r="T41" s="47"/>
       <c r="U41" s="47"/>
       <c r="V41" s="47"/>
-      <c r="AC41" s="47"/>
+      <c r="W41" s="47"/>
       <c r="AD41" s="47"/>
       <c r="AE41" s="47"/>
       <c r="AF41" s="47"/>
       <c r="AG41" s="47"/>
-    </row>
-    <row r="42" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH41" s="47"/>
+    </row>
+    <row r="42" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B42" s="126"/>
       <c r="C42" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="94" t="s">
+      <c r="D42" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E42" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="E42" s="95"/>
-      <c r="F42" s="83" t="s">
+      <c r="F42" s="95"/>
+      <c r="G42" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G42" s="85" t="s">
+      <c r="H42" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H42" s="81">
+      <c r="I42" s="81">
         <v>16</v>
       </c>
-      <c r="I42" s="81" t="s">
+      <c r="J42" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J42" s="85"/>
-      <c r="K42" s="142">
+      <c r="K42" s="85"/>
+      <c r="L42" s="142">
         <v>14</v>
       </c>
-      <c r="L42" s="121">
+      <c r="M42" s="121">
         <v>5.25</v>
       </c>
-      <c r="M42" s="121">
+      <c r="N42" s="121">
         <v>84</v>
       </c>
-      <c r="N42" s="85"/>
-      <c r="P42" s="47"/>
+      <c r="O42" s="85"/>
       <c r="Q42" s="47"/>
       <c r="R42" s="47"/>
       <c r="S42" s="47"/>
       <c r="T42" s="47"/>
       <c r="U42" s="47"/>
       <c r="V42" s="47"/>
-      <c r="AC42" s="47"/>
+      <c r="W42" s="47"/>
       <c r="AD42" s="47"/>
       <c r="AE42" s="47"/>
       <c r="AF42" s="47"/>
       <c r="AG42" s="47"/>
-    </row>
-    <row r="43" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH42" s="47"/>
+    </row>
+    <row r="43" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B43" s="126"/>
       <c r="C43" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="94" t="s">
+      <c r="D43" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E43" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="95"/>
-      <c r="F43" s="83" t="s">
+      <c r="F43" s="95"/>
+      <c r="G43" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G43" s="85" t="s">
+      <c r="H43" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H43" s="81">
+      <c r="I43" s="81">
         <v>72</v>
       </c>
-      <c r="I43" s="81" t="s">
+      <c r="J43" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J43" s="85"/>
-      <c r="K43" s="142">
+      <c r="K43" s="85"/>
+      <c r="L43" s="142">
         <v>129</v>
       </c>
-      <c r="L43" s="121">
+      <c r="M43" s="121">
         <v>10.881944444444445</v>
       </c>
-      <c r="M43" s="121">
+      <c r="N43" s="121">
         <v>783.5</v>
       </c>
-      <c r="N43" s="85"/>
-      <c r="P43" s="47"/>
+      <c r="O43" s="85"/>
       <c r="Q43" s="47"/>
       <c r="R43" s="47"/>
       <c r="S43" s="47"/>
       <c r="T43" s="47"/>
       <c r="U43" s="47"/>
       <c r="V43" s="47"/>
-      <c r="AC43" s="47"/>
+      <c r="W43" s="47"/>
       <c r="AD43" s="47"/>
       <c r="AE43" s="47"/>
       <c r="AF43" s="47"/>
       <c r="AG43" s="47"/>
-    </row>
-    <row r="44" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH43" s="47"/>
+    </row>
+    <row r="44" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B44" s="126"/>
       <c r="C44" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="94" t="s">
+      <c r="D44" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="95"/>
-      <c r="F44" s="83" t="s">
+      <c r="F44" s="95"/>
+      <c r="G44" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G44" s="85" t="s">
+      <c r="H44" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H44" s="81">
+      <c r="I44" s="81">
         <v>40</v>
       </c>
-      <c r="I44" s="81" t="s">
+      <c r="J44" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J44" s="85"/>
-      <c r="K44" s="142">
+      <c r="K44" s="85"/>
+      <c r="L44" s="142">
         <v>32</v>
       </c>
-      <c r="L44" s="121">
+      <c r="M44" s="121">
         <v>4.8287037037037033</v>
       </c>
-      <c r="M44" s="121">
+      <c r="N44" s="121">
         <v>193.14814814814812</v>
       </c>
-      <c r="N44" s="85"/>
-      <c r="P44" s="47"/>
+      <c r="O44" s="85"/>
       <c r="Q44" s="47"/>
       <c r="R44" s="47"/>
       <c r="S44" s="47"/>
       <c r="T44" s="47"/>
       <c r="U44" s="47"/>
       <c r="V44" s="47"/>
-      <c r="AC44" s="47"/>
+      <c r="W44" s="47"/>
       <c r="AD44" s="47"/>
       <c r="AE44" s="47"/>
       <c r="AF44" s="47"/>
       <c r="AG44" s="47"/>
-    </row>
-    <row r="45" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH44" s="47"/>
+    </row>
+    <row r="45" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B45" s="126"/>
       <c r="C45" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D45" s="94" t="s">
+      <c r="D45" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="95"/>
-      <c r="F45" s="83" t="s">
+      <c r="F45" s="95"/>
+      <c r="G45" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G45" s="85" t="s">
+      <c r="H45" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H45" s="81">
+      <c r="I45" s="81">
         <v>160</v>
       </c>
-      <c r="I45" s="81" t="s">
+      <c r="J45" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J45" s="85"/>
-      <c r="K45" s="142">
+      <c r="K45" s="85"/>
+      <c r="L45" s="142">
         <v>128</v>
       </c>
-      <c r="L45" s="121">
+      <c r="M45" s="121">
         <v>4.8287037037037033</v>
       </c>
-      <c r="M45" s="121">
+      <c r="N45" s="121">
         <v>772.5925925925925</v>
       </c>
-      <c r="N45" s="85"/>
-      <c r="P45" s="47"/>
+      <c r="O45" s="85"/>
       <c r="Q45" s="47"/>
       <c r="R45" s="47"/>
       <c r="S45" s="47"/>
       <c r="T45" s="47"/>
       <c r="U45" s="47"/>
       <c r="V45" s="47"/>
-      <c r="AC45" s="47"/>
+      <c r="W45" s="47"/>
       <c r="AD45" s="47"/>
       <c r="AE45" s="47"/>
       <c r="AF45" s="47"/>
       <c r="AG45" s="47"/>
-    </row>
-    <row r="46" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH45" s="47"/>
+    </row>
+    <row r="46" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B46" s="126"/>
       <c r="C46" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="96" t="s">
+      <c r="D46" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E46" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="95"/>
-      <c r="F46" s="83" t="s">
+      <c r="F46" s="95"/>
+      <c r="G46" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="85" t="s">
+      <c r="H46" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H46" s="81">
+      <c r="I46" s="81">
         <v>16</v>
       </c>
-      <c r="I46" s="81" t="s">
+      <c r="J46" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J46" s="85"/>
-      <c r="K46" s="142">
+      <c r="K46" s="85"/>
+      <c r="L46" s="142">
         <v>12</v>
       </c>
-      <c r="L46" s="121">
+      <c r="M46" s="121">
         <v>4.8287037037037033</v>
       </c>
-      <c r="M46" s="121">
+      <c r="N46" s="121">
         <v>77.259259259259252</v>
       </c>
-      <c r="N46" s="85"/>
-      <c r="P46" s="47"/>
+      <c r="O46" s="85"/>
       <c r="Q46" s="47"/>
       <c r="R46" s="47"/>
       <c r="S46" s="47"/>
       <c r="T46" s="47"/>
       <c r="U46" s="47"/>
       <c r="V46" s="47"/>
-      <c r="AC46" s="47"/>
+      <c r="W46" s="47"/>
       <c r="AD46" s="47"/>
       <c r="AE46" s="47"/>
       <c r="AF46" s="47"/>
       <c r="AG46" s="47"/>
-    </row>
-    <row r="47" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH46" s="47"/>
+    </row>
+    <row r="47" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B47" s="129">
         <v>8</v>
       </c>
       <c r="C47" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="130" t="s">
+      <c r="D47" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E47" s="131"/>
-      <c r="F47" s="129" t="s">
+      <c r="F47" s="131"/>
+      <c r="G47" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="G47" s="132" t="s">
+      <c r="H47" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H47" s="133">
+      <c r="I47" s="133">
         <v>1</v>
       </c>
-      <c r="I47" s="133" t="s">
+      <c r="J47" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="134" t="s">
+      <c r="K47" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="143">
+      <c r="L47" s="143">
         <v>2640</v>
       </c>
-      <c r="L47" s="135"/>
-      <c r="M47" s="135">
+      <c r="M47" s="135"/>
+      <c r="N47" s="135">
         <v>15172.5</v>
       </c>
-      <c r="N47" s="132" t="s">
+      <c r="O47" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="P47" s="47"/>
       <c r="Q47" s="47"/>
       <c r="R47" s="47"/>
       <c r="S47" s="47"/>
       <c r="T47" s="47"/>
       <c r="U47" s="47"/>
       <c r="V47" s="47"/>
-      <c r="AC47" s="47"/>
+      <c r="W47" s="47"/>
       <c r="AD47" s="47"/>
       <c r="AE47" s="47"/>
       <c r="AF47" s="47"/>
       <c r="AG47" s="47"/>
-    </row>
-    <row r="48" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH47" s="47"/>
+    </row>
+    <row r="48" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B48" s="126"/>
       <c r="C48" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D48" s="94" t="s">
+      <c r="D48" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E48" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="E48" s="95"/>
-      <c r="F48" s="83" t="s">
+      <c r="F48" s="95"/>
+      <c r="G48" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G48" s="85" t="s">
+      <c r="H48" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H48" s="81">
+      <c r="I48" s="81">
         <v>40</v>
       </c>
-      <c r="I48" s="81" t="s">
+      <c r="J48" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J48" s="101"/>
-      <c r="K48" s="142">
+      <c r="K48" s="101"/>
+      <c r="L48" s="142">
         <v>444</v>
       </c>
-      <c r="L48" s="121">
+      <c r="M48" s="121">
         <v>64</v>
       </c>
-      <c r="M48" s="121">
+      <c r="N48" s="121">
         <v>2560</v>
       </c>
-      <c r="N48" s="85"/>
-      <c r="P48" s="47"/>
+      <c r="O48" s="85"/>
       <c r="Q48" s="47"/>
       <c r="R48" s="47"/>
       <c r="S48" s="47"/>
       <c r="T48" s="47"/>
       <c r="U48" s="47"/>
       <c r="V48" s="47"/>
-      <c r="AC48" s="47"/>
+      <c r="W48" s="47"/>
       <c r="AD48" s="47"/>
       <c r="AE48" s="47"/>
       <c r="AF48" s="47"/>
       <c r="AG48" s="47"/>
-    </row>
-    <row r="49" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH48" s="47"/>
+    </row>
+    <row r="49" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B49" s="83"/>
       <c r="C49" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="96" t="s">
+      <c r="D49" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E49" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="95"/>
-      <c r="F49" s="83" t="s">
+      <c r="F49" s="95"/>
+      <c r="G49" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G49" s="85" t="s">
+      <c r="H49" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H49" s="81">
+      <c r="I49" s="81">
         <v>160</v>
       </c>
-      <c r="I49" s="81" t="s">
+      <c r="J49" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="85"/>
-      <c r="K49" s="142">
+      <c r="K49" s="85"/>
+      <c r="L49" s="142">
         <v>1920</v>
       </c>
-      <c r="L49" s="121">
+      <c r="M49" s="121">
         <v>68</v>
       </c>
-      <c r="M49" s="121">
+      <c r="N49" s="121">
         <v>10880</v>
       </c>
-      <c r="N49" s="85"/>
-      <c r="P49" s="47"/>
+      <c r="O49" s="85"/>
       <c r="Q49" s="47"/>
       <c r="R49" s="47"/>
       <c r="S49" s="47"/>
       <c r="T49" s="47"/>
       <c r="U49" s="47"/>
       <c r="V49" s="47"/>
-      <c r="AC49" s="47"/>
+      <c r="W49" s="47"/>
       <c r="AD49" s="47"/>
       <c r="AE49" s="47"/>
       <c r="AF49" s="47"/>
       <c r="AG49" s="47"/>
-    </row>
-    <row r="50" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH49" s="47"/>
+    </row>
+    <row r="50" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B50" s="83"/>
       <c r="C50" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D50" s="96" t="s">
+      <c r="D50" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="95"/>
-      <c r="F50" s="83" t="s">
+      <c r="F50" s="95"/>
+      <c r="G50" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G50" s="85" t="s">
+      <c r="H50" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H50" s="81">
+      <c r="I50" s="81">
         <v>16</v>
       </c>
-      <c r="I50" s="81" t="s">
+      <c r="J50" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J50" s="85"/>
-      <c r="K50" s="142">
+      <c r="K50" s="85"/>
+      <c r="L50" s="142">
         <v>104</v>
       </c>
-      <c r="L50" s="121">
+      <c r="M50" s="121">
         <v>40</v>
       </c>
-      <c r="M50" s="121">
+      <c r="N50" s="121">
         <v>640</v>
       </c>
-      <c r="N50" s="85"/>
-      <c r="P50" s="47"/>
+      <c r="O50" s="85"/>
       <c r="Q50" s="47"/>
       <c r="R50" s="47"/>
       <c r="S50" s="47"/>
       <c r="T50" s="47"/>
       <c r="U50" s="47"/>
       <c r="V50" s="47"/>
-      <c r="AC50" s="47"/>
+      <c r="W50" s="47"/>
       <c r="AD50" s="47"/>
       <c r="AE50" s="47"/>
       <c r="AF50" s="47"/>
       <c r="AG50" s="47"/>
-    </row>
-    <row r="51" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH50" s="47"/>
+    </row>
+    <row r="51" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B51" s="83"/>
       <c r="C51" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D51" s="94" t="s">
+      <c r="D51" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E51" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="E51" s="95"/>
-      <c r="F51" s="83" t="s">
+      <c r="F51" s="95"/>
+      <c r="G51" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G51" s="85" t="s">
+      <c r="H51" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H51" s="81">
+      <c r="I51" s="81">
         <v>40</v>
       </c>
-      <c r="I51" s="81" t="s">
+      <c r="J51" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J51" s="85"/>
-      <c r="K51" s="142">
+      <c r="K51" s="85"/>
+      <c r="L51" s="142">
         <v>32</v>
       </c>
-      <c r="L51" s="121">
+      <c r="M51" s="121">
         <v>4.75</v>
       </c>
-      <c r="M51" s="121">
+      <c r="N51" s="121">
         <v>190</v>
       </c>
-      <c r="N51" s="85"/>
-      <c r="P51" s="47"/>
+      <c r="O51" s="85"/>
       <c r="Q51" s="47"/>
       <c r="R51" s="47"/>
       <c r="S51" s="47"/>
       <c r="T51" s="47"/>
       <c r="U51" s="47"/>
       <c r="V51" s="47"/>
-      <c r="AC51" s="47"/>
+      <c r="W51" s="47"/>
       <c r="AD51" s="47"/>
       <c r="AE51" s="47"/>
       <c r="AF51" s="47"/>
       <c r="AG51" s="47"/>
-    </row>
-    <row r="52" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH51" s="47"/>
+    </row>
+    <row r="52" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B52" s="83"/>
       <c r="C52" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D52" s="94" t="s">
+      <c r="D52" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E52" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="E52" s="95"/>
-      <c r="F52" s="83" t="s">
+      <c r="F52" s="95"/>
+      <c r="G52" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G52" s="85" t="s">
+      <c r="H52" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H52" s="81">
+      <c r="I52" s="81">
         <v>160</v>
       </c>
-      <c r="I52" s="81" t="s">
+      <c r="J52" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J52" s="85"/>
-      <c r="K52" s="142">
+      <c r="K52" s="85"/>
+      <c r="L52" s="142">
         <v>128</v>
       </c>
-      <c r="L52" s="121">
+      <c r="M52" s="121">
         <v>5.1906249999999998</v>
       </c>
-      <c r="M52" s="121">
+      <c r="N52" s="121">
         <v>830.5</v>
       </c>
-      <c r="N52" s="85"/>
-      <c r="P52" s="47"/>
+      <c r="O52" s="85"/>
       <c r="Q52" s="47"/>
       <c r="R52" s="47"/>
       <c r="S52" s="47"/>
       <c r="T52" s="47"/>
       <c r="U52" s="47"/>
       <c r="V52" s="47"/>
-      <c r="AC52" s="47"/>
+      <c r="W52" s="47"/>
       <c r="AD52" s="47"/>
       <c r="AE52" s="47"/>
       <c r="AF52" s="47"/>
       <c r="AG52" s="47"/>
-    </row>
-    <row r="53" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH52" s="47"/>
+    </row>
+    <row r="53" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B53" s="83"/>
       <c r="C53" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="94" t="s">
+      <c r="D53" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="95"/>
-      <c r="F53" s="83" t="s">
+      <c r="F53" s="95"/>
+      <c r="G53" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G53" s="85" t="s">
+      <c r="H53" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H53" s="81">
+      <c r="I53" s="81">
         <v>16</v>
       </c>
-      <c r="I53" s="81" t="s">
+      <c r="J53" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J53" s="85"/>
-      <c r="K53" s="142">
+      <c r="K53" s="85"/>
+      <c r="L53" s="142">
         <v>12</v>
       </c>
-      <c r="L53" s="121">
+      <c r="M53" s="121">
         <v>4.5</v>
       </c>
-      <c r="M53" s="121">
+      <c r="N53" s="121">
         <v>72</v>
       </c>
-      <c r="N53" s="85"/>
-      <c r="P53" s="47"/>
+      <c r="O53" s="85"/>
       <c r="Q53" s="47"/>
       <c r="R53" s="47"/>
       <c r="S53" s="47"/>
       <c r="T53" s="47"/>
       <c r="U53" s="47"/>
       <c r="V53" s="47"/>
-      <c r="AC53" s="47"/>
+      <c r="W53" s="47"/>
       <c r="AD53" s="47"/>
       <c r="AE53" s="47"/>
       <c r="AF53" s="47"/>
       <c r="AG53" s="47"/>
-    </row>
-    <row r="54" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH53" s="47"/>
+    </row>
+    <row r="54" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B54" s="129">
         <v>9</v>
       </c>
       <c r="C54" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="D54" s="130" t="s">
+      <c r="D54" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="131"/>
-      <c r="F54" s="129" t="s">
+      <c r="F54" s="131"/>
+      <c r="G54" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="G54" s="132" t="s">
+      <c r="H54" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H54" s="133">
+      <c r="I54" s="133">
         <v>1</v>
       </c>
-      <c r="I54" s="133" t="s">
+      <c r="J54" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="134" t="s">
+      <c r="K54" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="K54" s="143">
+      <c r="L54" s="143">
         <v>155</v>
       </c>
-      <c r="L54" s="135"/>
-      <c r="M54" s="135">
+      <c r="M54" s="135"/>
+      <c r="N54" s="135">
         <v>1213.5</v>
       </c>
-      <c r="N54" s="132" t="s">
+      <c r="O54" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="P54" s="47"/>
       <c r="Q54" s="47"/>
       <c r="R54" s="47"/>
       <c r="S54" s="47"/>
       <c r="T54" s="47"/>
       <c r="U54" s="47"/>
       <c r="V54" s="47"/>
-      <c r="AC54" s="47"/>
+      <c r="W54" s="47"/>
       <c r="AD54" s="47"/>
       <c r="AE54" s="47"/>
       <c r="AF54" s="47"/>
       <c r="AG54" s="47"/>
-    </row>
-    <row r="55" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH54" s="47"/>
+    </row>
+    <row r="55" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B55" s="83"/>
       <c r="C55" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="94" t="s">
+      <c r="D55" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E55" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="E55" s="95"/>
-      <c r="F55" s="83" t="s">
+      <c r="F55" s="95"/>
+      <c r="G55" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G55" s="85" t="s">
+      <c r="H55" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H55" s="81">
+      <c r="I55" s="81">
         <v>8</v>
       </c>
-      <c r="I55" s="81" t="s">
+      <c r="J55" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J55" s="101"/>
-      <c r="K55" s="142">
+      <c r="K55" s="101"/>
+      <c r="L55" s="142">
         <v>14</v>
       </c>
-      <c r="L55" s="121">
+      <c r="M55" s="121">
         <v>15.4375</v>
       </c>
-      <c r="M55" s="121">
+      <c r="N55" s="121">
         <v>123.5</v>
       </c>
-      <c r="N55" s="85"/>
-      <c r="P55" s="47"/>
+      <c r="O55" s="85"/>
       <c r="Q55" s="47"/>
       <c r="R55" s="47"/>
       <c r="S55" s="47"/>
       <c r="T55" s="47"/>
       <c r="U55" s="47"/>
       <c r="V55" s="47"/>
-      <c r="AC55" s="47"/>
+      <c r="W55" s="47"/>
       <c r="AD55" s="47"/>
       <c r="AE55" s="47"/>
       <c r="AF55" s="47"/>
       <c r="AG55" s="47"/>
-    </row>
-    <row r="56" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH55" s="47"/>
+    </row>
+    <row r="56" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B56" s="83"/>
       <c r="C56" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D56" s="94" t="s">
+      <c r="D56" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E56" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="E56" s="95"/>
-      <c r="F56" s="83" t="s">
+      <c r="F56" s="95"/>
+      <c r="G56" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G56" s="85" t="s">
+      <c r="H56" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H56" s="81">
+      <c r="I56" s="81">
         <v>32</v>
       </c>
-      <c r="I56" s="81" t="s">
+      <c r="J56" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J56" s="85"/>
-      <c r="K56" s="142">
+      <c r="K56" s="85"/>
+      <c r="L56" s="142">
         <v>70</v>
       </c>
-      <c r="L56" s="121">
+      <c r="M56" s="121">
         <v>18.9375</v>
       </c>
-      <c r="M56" s="121">
+      <c r="N56" s="121">
         <v>606</v>
       </c>
-      <c r="N56" s="85"/>
-      <c r="P56" s="47"/>
+      <c r="O56" s="85"/>
       <c r="Q56" s="47"/>
       <c r="R56" s="47"/>
       <c r="S56" s="47"/>
       <c r="T56" s="47"/>
       <c r="U56" s="47"/>
       <c r="V56" s="47"/>
-      <c r="AC56" s="47"/>
+      <c r="W56" s="47"/>
       <c r="AD56" s="47"/>
       <c r="AE56" s="47"/>
       <c r="AF56" s="47"/>
       <c r="AG56" s="47"/>
-    </row>
-    <row r="57" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH56" s="47"/>
+    </row>
+    <row r="57" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B57" s="83"/>
       <c r="C57" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D57" s="94" t="s">
+      <c r="D57" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E57" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="E57" s="95"/>
-      <c r="F57" s="83" t="s">
+      <c r="F57" s="95"/>
+      <c r="G57" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G57" s="85" t="s">
+      <c r="H57" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H57" s="81">
+      <c r="I57" s="81">
         <v>5</v>
       </c>
-      <c r="I57" s="81" t="s">
+      <c r="J57" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J57" s="85"/>
-      <c r="K57" s="142">
+      <c r="K57" s="85"/>
+      <c r="L57" s="142">
         <v>3</v>
       </c>
-      <c r="L57" s="121">
+      <c r="M57" s="121">
         <v>5</v>
       </c>
-      <c r="M57" s="121">
+      <c r="N57" s="121">
         <v>25</v>
       </c>
-      <c r="N57" s="85"/>
-      <c r="P57" s="47"/>
+      <c r="O57" s="85"/>
       <c r="Q57" s="47"/>
       <c r="R57" s="47"/>
       <c r="S57" s="47"/>
       <c r="T57" s="47"/>
       <c r="U57" s="47"/>
       <c r="V57" s="47"/>
-      <c r="AC57" s="47"/>
+      <c r="W57" s="47"/>
       <c r="AD57" s="47"/>
       <c r="AE57" s="47"/>
       <c r="AF57" s="47"/>
       <c r="AG57" s="47"/>
-    </row>
-    <row r="58" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH57" s="47"/>
+    </row>
+    <row r="58" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B58" s="83"/>
       <c r="C58" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D58" s="94" t="s">
+      <c r="D58" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E58" s="95"/>
-      <c r="F58" s="83" t="s">
+      <c r="F58" s="95"/>
+      <c r="G58" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G58" s="85" t="s">
+      <c r="H58" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H58" s="81">
+      <c r="I58" s="81">
         <v>14</v>
       </c>
-      <c r="I58" s="81" t="s">
+      <c r="J58" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J58" s="85"/>
-      <c r="K58" s="142">
+      <c r="K58" s="85"/>
+      <c r="L58" s="142">
         <v>16</v>
       </c>
-      <c r="L58" s="121">
+      <c r="M58" s="121">
         <v>9.8571428571428577</v>
       </c>
-      <c r="M58" s="121">
+      <c r="N58" s="121">
         <v>138</v>
       </c>
-      <c r="N58" s="85"/>
-      <c r="P58" s="47"/>
+      <c r="O58" s="85"/>
       <c r="Q58" s="47"/>
       <c r="R58" s="47"/>
       <c r="S58" s="47"/>
       <c r="T58" s="47"/>
       <c r="U58" s="47"/>
       <c r="V58" s="47"/>
-      <c r="AC58" s="47"/>
+      <c r="W58" s="47"/>
       <c r="AD58" s="47"/>
       <c r="AE58" s="47"/>
       <c r="AF58" s="47"/>
       <c r="AG58" s="47"/>
-    </row>
-    <row r="59" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH58" s="47"/>
+    </row>
+    <row r="59" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B59" s="83"/>
       <c r="C59" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D59" s="94" t="s">
+      <c r="D59" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E59" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="95"/>
-      <c r="F59" s="83" t="s">
+      <c r="F59" s="95"/>
+      <c r="G59" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G59" s="85" t="s">
+      <c r="H59" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H59" s="81">
+      <c r="I59" s="81">
         <v>5</v>
       </c>
-      <c r="I59" s="81" t="s">
+      <c r="J59" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J59" s="85"/>
-      <c r="K59" s="142">
+      <c r="K59" s="85"/>
+      <c r="L59" s="142">
         <v>16</v>
       </c>
-      <c r="L59" s="121">
+      <c r="M59" s="121">
         <v>20</v>
       </c>
-      <c r="M59" s="121">
+      <c r="N59" s="121">
         <v>100</v>
       </c>
-      <c r="N59" s="85"/>
-      <c r="P59" s="47"/>
-      <c r="Q59" s="157"/>
-      <c r="R59" s="47"/>
+      <c r="O59" s="85"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="157"/>
       <c r="S59" s="47"/>
       <c r="T59" s="47"/>
       <c r="U59" s="47"/>
       <c r="V59" s="47"/>
-      <c r="AC59" s="47"/>
+      <c r="W59" s="47"/>
       <c r="AD59" s="47"/>
       <c r="AE59" s="47"/>
       <c r="AF59" s="47"/>
       <c r="AG59" s="47"/>
-    </row>
-    <row r="60" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH59" s="47"/>
+    </row>
+    <row r="60" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B60" s="83"/>
       <c r="C60" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D60" s="94" t="s">
+      <c r="D60" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E60" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="95"/>
-      <c r="F60" s="83" t="s">
+      <c r="F60" s="95"/>
+      <c r="G60" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G60" s="85" t="s">
+      <c r="H60" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H60" s="81">
+      <c r="I60" s="81">
         <v>8</v>
       </c>
-      <c r="I60" s="81" t="s">
+      <c r="J60" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J60" s="85"/>
-      <c r="K60" s="142">
+      <c r="K60" s="85"/>
+      <c r="L60" s="142">
         <v>21</v>
       </c>
-      <c r="L60" s="121">
+      <c r="M60" s="121">
         <v>16.345238095238095</v>
       </c>
-      <c r="M60" s="121">
+      <c r="N60" s="121">
         <v>130.76190476190476</v>
       </c>
-      <c r="N60" s="85"/>
-      <c r="P60" s="47"/>
+      <c r="O60" s="85"/>
       <c r="Q60" s="47"/>
       <c r="R60" s="47"/>
       <c r="S60" s="47"/>
       <c r="T60" s="47"/>
       <c r="U60" s="47"/>
       <c r="V60" s="47"/>
-      <c r="AC60" s="47"/>
+      <c r="W60" s="47"/>
       <c r="AD60" s="47"/>
       <c r="AE60" s="47"/>
       <c r="AF60" s="47"/>
       <c r="AG60" s="47"/>
-    </row>
-    <row r="61" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH60" s="47"/>
+    </row>
+    <row r="61" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B61" s="83"/>
       <c r="C61" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="94" t="s">
+      <c r="D61" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E61" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="95"/>
-      <c r="F61" s="83" t="s">
+      <c r="F61" s="95"/>
+      <c r="G61" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G61" s="85" t="s">
+      <c r="H61" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H61" s="81">
+      <c r="I61" s="81">
         <v>5</v>
       </c>
-      <c r="I61" s="81" t="s">
+      <c r="J61" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J61" s="85"/>
-      <c r="K61" s="142">
+      <c r="K61" s="85"/>
+      <c r="L61" s="142">
         <v>6</v>
       </c>
-      <c r="L61" s="121">
+      <c r="M61" s="121">
         <v>7.1904761904761907</v>
       </c>
-      <c r="M61" s="121">
+      <c r="N61" s="121">
         <v>35.952380952380956</v>
       </c>
-      <c r="N61" s="85"/>
-      <c r="P61" s="47"/>
+      <c r="O61" s="85"/>
       <c r="Q61" s="47"/>
       <c r="R61" s="47"/>
       <c r="S61" s="47"/>
       <c r="T61" s="47"/>
       <c r="U61" s="47"/>
       <c r="V61" s="47"/>
-      <c r="AC61" s="47"/>
+      <c r="W61" s="47"/>
       <c r="AD61" s="47"/>
       <c r="AE61" s="47"/>
       <c r="AF61" s="47"/>
       <c r="AG61" s="47"/>
-    </row>
-    <row r="62" spans="2:33" s="48" customFormat="1" ht="28.5" customHeight="1">
+      <c r="AH61" s="47"/>
+    </row>
+    <row r="62" spans="2:34" s="48" customFormat="1" ht="28.5" customHeight="1">
       <c r="B62" s="83"/>
       <c r="C62" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D62" s="94" t="s">
+      <c r="D62" s="126" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="95"/>
-      <c r="F62" s="83" t="s">
+      <c r="F62" s="95"/>
+      <c r="G62" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G62" s="85" t="s">
+      <c r="H62" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="H62" s="81">
+      <c r="I62" s="81">
         <v>5</v>
       </c>
-      <c r="I62" s="81" t="s">
+      <c r="J62" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="J62" s="85"/>
-      <c r="K62" s="142">
+      <c r="K62" s="85"/>
+      <c r="L62" s="142">
         <v>9</v>
       </c>
-      <c r="L62" s="121">
+      <c r="M62" s="121">
         <v>10.857142857142858</v>
       </c>
-      <c r="M62" s="121">
+      <c r="N62" s="121">
         <v>54.285714285714292</v>
       </c>
-      <c r="N62" s="85"/>
-      <c r="P62" s="47"/>
+      <c r="O62" s="85"/>
       <c r="Q62" s="47"/>
       <c r="R62" s="47"/>
       <c r="S62" s="47"/>
       <c r="T62" s="47"/>
       <c r="U62" s="47"/>
       <c r="V62" s="47"/>
-      <c r="AC62" s="47"/>
+      <c r="W62" s="47"/>
       <c r="AD62" s="47"/>
       <c r="AE62" s="47"/>
       <c r="AF62" s="47"/>
       <c r="AG62" s="47"/>
-    </row>
-    <row r="63" spans="2:33" s="6" customFormat="1" ht="23.25" customHeight="1">
-      <c r="B63" s="213" t="s">
+      <c r="AH62" s="47"/>
+    </row>
+    <row r="63" spans="2:34" s="6" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B63" s="196" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="213"/>
-      <c r="D63" s="213"/>
-      <c r="E63" s="213"/>
-      <c r="F63" s="213"/>
-      <c r="G63" s="213"/>
-      <c r="H63" s="213"/>
-      <c r="I63" s="213"/>
-      <c r="J63" s="127"/>
-      <c r="K63" s="49"/>
-      <c r="L63" s="128"/>
-      <c r="M63" s="181">
-        <f>SUM(M10:M62)-M10-M18-M23-M26-M29-M32-M35-M47-M54</f>
+      <c r="C63" s="196"/>
+      <c r="D63" s="196"/>
+      <c r="E63" s="196"/>
+      <c r="F63" s="196"/>
+      <c r="G63" s="196"/>
+      <c r="H63" s="196"/>
+      <c r="I63" s="196"/>
+      <c r="J63" s="196"/>
+      <c r="K63" s="127"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="128"/>
+      <c r="N63" s="181">
+        <f>SUM(N10:N62)-N10-N18-N23-N26-N29-N32-N35-N47-N54</f>
         <v>104999.99999999997</v>
       </c>
-      <c r="N63" s="127"/>
-      <c r="O63" s="41"/>
-      <c r="P63" s="10"/>
+      <c r="O63" s="127"/>
+      <c r="P63" s="41"/>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
       <c r="S63" s="10"/>
       <c r="T63" s="10"/>
       <c r="U63" s="10"/>
       <c r="V63" s="10"/>
-      <c r="AC63" s="10"/>
+      <c r="W63" s="10"/>
       <c r="AD63" s="10"/>
       <c r="AE63" s="10"/>
       <c r="AF63" s="10"/>
       <c r="AG63" s="10"/>
-    </row>
-    <row r="64" spans="2:33" ht="18" customHeight="1">
-      <c r="M64" s="180"/>
+      <c r="AH63" s="10"/>
+    </row>
+    <row r="64" spans="2:34" ht="18" customHeight="1">
+      <c r="N64" s="180"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="J8:J9"/>
+  <mergeCells count="19">
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B63:J63"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="N8:N9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="J6:L6"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
-  <conditionalFormatting sqref="D6">
+  <conditionalFormatting sqref="E6">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -6549,26 +6655,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:50" ht="9" customHeight="1">
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="208"/>
+      <c r="O1" s="208"/>
+      <c r="P1" s="208"/>
+      <c r="Q1" s="208"/>
+      <c r="R1" s="208"/>
+      <c r="S1" s="208"/>
+      <c r="T1" s="208"/>
+      <c r="U1" s="208"/>
     </row>
     <row r="2" spans="2:50" ht="26.1" customHeight="1">
       <c r="B2" s="29"/>
@@ -6606,17 +6712,17 @@
     </row>
     <row r="3" spans="2:50" ht="27.6" customHeight="1">
       <c r="B3" s="29"/>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
+      <c r="K3" s="209"/>
       <c r="L3" s="33"/>
       <c r="M3" s="34"/>
       <c r="N3" s="35"/>
@@ -6642,28 +6748,28 @@
       <c r="AN3" s="32"/>
     </row>
     <row r="4" spans="2:50" ht="33.75" customHeight="1">
-      <c r="B4" s="197" t="s">
+      <c r="B4" s="210" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="198"/>
-      <c r="I4" s="198"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="198"/>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="198"/>
-      <c r="O4" s="198"/>
-      <c r="P4" s="198"/>
-      <c r="Q4" s="198"/>
-      <c r="R4" s="198"/>
-      <c r="S4" s="198"/>
-      <c r="T4" s="198"/>
-      <c r="U4" s="199"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="211"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="211"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="211"/>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="211"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="212"/>
     </row>
     <row r="5" spans="2:50" s="6" customFormat="1" ht="17.25" customHeight="1">
       <c r="B5" s="10"/>
@@ -7193,54 +7299,54 @@
       <c r="AN12" s="10"/>
     </row>
     <row r="13" spans="2:50" s="48" customFormat="1" ht="20.25" customHeight="1">
-      <c r="B13" s="203" t="s">
+      <c r="B13" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="206" t="s">
+      <c r="C13" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="207" t="s">
+      <c r="D13" s="202" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="208"/>
-      <c r="F13" s="219" t="s">
+      <c r="E13" s="203"/>
+      <c r="F13" s="221" t="s">
         <v>122</v>
       </c>
-      <c r="G13" s="206" t="s">
+      <c r="G13" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="203" t="s">
+      <c r="H13" s="198" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="211" t="s">
+      <c r="I13" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="212"/>
-      <c r="K13" s="203" t="s">
+      <c r="J13" s="207"/>
+      <c r="K13" s="198" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="211" t="s">
+      <c r="L13" s="206" t="s">
         <v>102</v>
       </c>
-      <c r="M13" s="221"/>
-      <c r="N13" s="221"/>
-      <c r="O13" s="212"/>
-      <c r="P13" s="203" t="s">
+      <c r="M13" s="216"/>
+      <c r="N13" s="216"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="198" t="s">
         <v>103</v>
       </c>
-      <c r="Q13" s="203" t="s">
+      <c r="Q13" s="198" t="s">
         <v>104</v>
       </c>
-      <c r="R13" s="203" t="s">
+      <c r="R13" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="S13" s="203" t="s">
+      <c r="S13" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="T13" s="207" t="s">
+      <c r="T13" s="202" t="s">
         <v>123</v>
       </c>
-      <c r="U13" s="203" t="s">
+      <c r="U13" s="198" t="s">
         <v>19</v>
       </c>
       <c r="V13" s="46"/>
@@ -7258,20 +7364,20 @@
       <c r="AN13" s="47"/>
     </row>
     <row r="14" spans="2:50" s="48" customFormat="1" ht="28.5" customHeight="1">
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="220"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="204"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="199"/>
       <c r="I14" s="49" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="204"/>
+      <c r="K14" s="199"/>
       <c r="L14" s="50" t="s">
         <v>107</v>
       </c>
@@ -7284,12 +7390,12 @@
       <c r="O14" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="P14" s="204"/>
-      <c r="Q14" s="204"/>
-      <c r="R14" s="204"/>
-      <c r="S14" s="204"/>
-      <c r="T14" s="209"/>
-      <c r="U14" s="204"/>
+      <c r="P14" s="199"/>
+      <c r="Q14" s="199"/>
+      <c r="R14" s="199"/>
+      <c r="S14" s="199"/>
+      <c r="T14" s="204"/>
+      <c r="U14" s="199"/>
       <c r="W14" s="47"/>
       <c r="X14" s="47"/>
       <c r="Y14" s="47"/>
@@ -10235,15 +10341,15 @@
       <c r="AN67" s="47"/>
     </row>
     <row r="68" spans="2:40" s="53" customFormat="1" ht="24" customHeight="1">
-      <c r="B68" s="215" t="s">
+      <c r="B68" s="217" t="s">
         <v>164</v>
       </c>
-      <c r="C68" s="216"/>
-      <c r="D68" s="216"/>
-      <c r="E68" s="216"/>
-      <c r="F68" s="216"/>
-      <c r="G68" s="216"/>
-      <c r="H68" s="217"/>
+      <c r="C68" s="218"/>
+      <c r="D68" s="218"/>
+      <c r="E68" s="218"/>
+      <c r="F68" s="218"/>
+      <c r="G68" s="218"/>
+      <c r="H68" s="219"/>
       <c r="I68" s="102"/>
       <c r="J68" s="102"/>
       <c r="K68" s="103"/>
@@ -10271,17 +10377,17 @@
       <c r="AN68" s="52"/>
     </row>
     <row r="69" spans="2:40" s="6" customFormat="1" ht="32.25" customHeight="1">
-      <c r="B69" s="218" t="s">
+      <c r="B69" s="220" t="s">
         <v>66</v>
       </c>
-      <c r="C69" s="218"/>
-      <c r="D69" s="218"/>
-      <c r="E69" s="218"/>
-      <c r="F69" s="218"/>
-      <c r="G69" s="218"/>
-      <c r="H69" s="218"/>
-      <c r="I69" s="218"/>
-      <c r="J69" s="218"/>
+      <c r="C69" s="220"/>
+      <c r="D69" s="220"/>
+      <c r="E69" s="220"/>
+      <c r="F69" s="220"/>
+      <c r="G69" s="220"/>
+      <c r="H69" s="220"/>
+      <c r="I69" s="220"/>
+      <c r="J69" s="220"/>
       <c r="K69" s="81"/>
       <c r="L69" s="81"/>
       <c r="M69" s="164"/>
@@ -10325,6 +10431,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="F13:F14"/>
     <mergeCell ref="B1:U1"/>
     <mergeCell ref="C3:K3"/>
     <mergeCell ref="B4:U4"/>
@@ -10339,12 +10451,6 @@
     <mergeCell ref="S13:S14"/>
     <mergeCell ref="T13:T14"/>
     <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B69:J69"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="F13:F14"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10425,15 +10531,15 @@
     </row>
     <row r="3" spans="2:20" ht="27.6" customHeight="1" thickBot="1">
       <c r="B3" s="71"/>
-      <c r="C3" s="227" t="s">
+      <c r="C3" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="227"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="227"/>
-      <c r="G3" s="227"/>
-      <c r="H3" s="227"/>
-      <c r="I3" s="227"/>
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="228"/>
+      <c r="H3" s="228"/>
+      <c r="I3" s="228"/>
       <c r="J3" s="1"/>
       <c r="K3" s="67"/>
       <c r="L3" s="14"/>
@@ -10447,27 +10553,27 @@
       <c r="T3" s="71"/>
     </row>
     <row r="4" spans="2:20" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B4" s="228" t="s">
+      <c r="B4" s="229" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="229"/>
-      <c r="D4" s="229"/>
-      <c r="E4" s="229"/>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
-      <c r="H4" s="229"/>
-      <c r="I4" s="229"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="229"/>
-      <c r="Q4" s="229"/>
-      <c r="R4" s="229"/>
-      <c r="S4" s="229"/>
-      <c r="T4" s="230"/>
+      <c r="C4" s="230"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="231"/>
     </row>
     <row r="5" spans="2:20" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1">
       <c r="B5" s="5"/>
@@ -10709,68 +10815,68 @@
       <c r="T12" s="5"/>
     </row>
     <row r="13" spans="2:20" s="3" customFormat="1" ht="12.75">
-      <c r="B13" s="231" t="s">
+      <c r="B13" s="232" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="233" t="s">
+      <c r="C13" s="234" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="235" t="s">
+      <c r="D13" s="236" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="231" t="s">
+      <c r="E13" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="224" t="s">
+      <c r="F13" s="225" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="226"/>
-      <c r="H13" s="231" t="s">
+      <c r="G13" s="227"/>
+      <c r="H13" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="224" t="s">
+      <c r="I13" s="225" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="225"/>
-      <c r="K13" s="225"/>
-      <c r="L13" s="226"/>
-      <c r="M13" s="231" t="s">
+      <c r="J13" s="226"/>
+      <c r="K13" s="226"/>
+      <c r="L13" s="227"/>
+      <c r="M13" s="232" t="s">
         <v>103</v>
       </c>
-      <c r="N13" s="231" t="s">
+      <c r="N13" s="232" t="s">
         <v>104</v>
       </c>
-      <c r="O13" s="231" t="s">
+      <c r="O13" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="P13" s="222" t="s">
+      <c r="P13" s="223" t="s">
         <v>205</v>
       </c>
-      <c r="Q13" s="222" t="s">
+      <c r="Q13" s="223" t="s">
         <v>206</v>
       </c>
-      <c r="R13" s="222" t="s">
+      <c r="R13" s="223" t="s">
         <v>207</v>
       </c>
-      <c r="S13" s="231" t="s">
+      <c r="S13" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="T13" s="231" t="s">
+      <c r="T13" s="232" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="2:20" s="3" customFormat="1" ht="43.15" customHeight="1">
-      <c r="B14" s="232"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="236"/>
-      <c r="E14" s="232"/>
+      <c r="B14" s="233"/>
+      <c r="C14" s="235"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="233"/>
       <c r="F14" s="22" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="232"/>
+      <c r="H14" s="233"/>
       <c r="I14" s="23" t="s">
         <v>107</v>
       </c>
@@ -10783,22 +10889,22 @@
       <c r="L14" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="M14" s="232"/>
-      <c r="N14" s="232"/>
-      <c r="O14" s="232"/>
-      <c r="P14" s="223"/>
-      <c r="Q14" s="223"/>
-      <c r="R14" s="223"/>
-      <c r="S14" s="232"/>
-      <c r="T14" s="232"/>
+      <c r="M14" s="233"/>
+      <c r="N14" s="233"/>
+      <c r="O14" s="233"/>
+      <c r="P14" s="224"/>
+      <c r="Q14" s="224"/>
+      <c r="R14" s="224"/>
+      <c r="S14" s="233"/>
+      <c r="T14" s="233"/>
     </row>
     <row r="15" spans="2:20" s="2" customFormat="1" ht="47.25" customHeight="1">
       <c r="B15" s="82">
         <v>1</v>
       </c>
       <c r="C15" s="83" t="str">
-        <f>'Breakdown CI'!C10</f>
-        <v>OM4-DE-IS-0001-001</v>
+        <f>'Breakdown CI'!D10</f>
+        <v>S1</v>
       </c>
       <c r="D15" s="84" t="s">
         <v>204</v>
@@ -10977,8 +11083,8 @@
         <v>4</v>
       </c>
       <c r="C18" s="83" t="str">
-        <f>'Breakdown CI'!C26</f>
-        <v>OM4-DE-IS-0001-004</v>
+        <f>'Breakdown CI'!D26</f>
+        <v>S1</v>
       </c>
       <c r="D18" s="84" t="s">
         <v>36</v>
@@ -11039,8 +11145,8 @@
         <v>5</v>
       </c>
       <c r="C19" s="83" t="str">
-        <f>'Breakdown CI'!C29</f>
-        <v>OM4-DE-IS-0001-005</v>
+        <f>'Breakdown CI'!D29</f>
+        <v>S1</v>
       </c>
       <c r="D19" s="84" t="s">
         <v>36</v>
@@ -11101,8 +11207,8 @@
         <v>6</v>
       </c>
       <c r="C20" s="83" t="str">
-        <f>'Breakdown CI'!C32</f>
-        <v>OM4-DE-IS-0001-006</v>
+        <f>'Breakdown CI'!D32</f>
+        <v>S1</v>
       </c>
       <c r="D20" s="84" t="s">
         <v>36</v>
@@ -11161,8 +11267,8 @@
         <v>7</v>
       </c>
       <c r="C21" s="83" t="str">
-        <f>'Breakdown CI'!C35</f>
-        <v>OM4-DE-IS-0001-007</v>
+        <f>'Breakdown CI'!D35</f>
+        <v>S1</v>
       </c>
       <c r="D21" s="84" t="s">
         <v>36</v>
@@ -11221,8 +11327,8 @@
         <v>8</v>
       </c>
       <c r="C22" s="83" t="str">
-        <f>'Breakdown CI'!C47</f>
-        <v>OM4-DE-IS-0001-008</v>
+        <f>'Breakdown CI'!D47</f>
+        <v>S1</v>
       </c>
       <c r="D22" s="84" t="s">
         <v>36</v>
@@ -11281,8 +11387,8 @@
         <v>9</v>
       </c>
       <c r="C23" s="83" t="str">
-        <f>'Breakdown CI'!C54</f>
-        <v>OM4-DE-IS-0001-009</v>
+        <f>'Breakdown CI'!D54</f>
+        <v>S1</v>
       </c>
       <c r="D23" s="84" t="s">
         <v>61</v>
@@ -11337,18 +11443,18 @@
       </c>
     </row>
     <row r="24" spans="2:20" ht="18.75" customHeight="1">
-      <c r="B24" s="224" t="s">
+      <c r="B24" s="225" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="225"/>
-      <c r="D24" s="225"/>
-      <c r="E24" s="225"/>
-      <c r="F24" s="225"/>
-      <c r="G24" s="225"/>
-      <c r="H24" s="225"/>
-      <c r="I24" s="225"/>
-      <c r="J24" s="225"/>
-      <c r="K24" s="226"/>
+      <c r="C24" s="226"/>
+      <c r="D24" s="226"/>
+      <c r="E24" s="226"/>
+      <c r="F24" s="226"/>
+      <c r="G24" s="226"/>
+      <c r="H24" s="226"/>
+      <c r="I24" s="226"/>
+      <c r="J24" s="226"/>
+      <c r="K24" s="227"/>
       <c r="L24" s="160">
         <f>SUM(L15:L23)</f>
         <v>20.131250000000001</v>
@@ -11410,6 +11516,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
     <mergeCell ref="P13:P14"/>
     <mergeCell ref="Q13:Q14"/>
     <mergeCell ref="R13:R14"/>
@@ -11426,8 +11534,6 @@
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="O13:O14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -11466,46 +11572,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="91.15" customHeight="1" thickBot="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="186" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
     </row>
     <row r="2" spans="1:13" ht="32.65" customHeight="1">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="187" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="188"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="189"/>
     </row>
     <row r="3" spans="1:13" ht="28.15" customHeight="1">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="190" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="191"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="192"/>
     </row>
     <row r="4" spans="1:13" s="59" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="105" t="s">
@@ -11514,16 +11620,16 @@
       <c r="B4" s="106" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="194"/>
+      <c r="I4" s="194"/>
+      <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:13" s="59" customFormat="1" ht="55.5" customHeight="1">
       <c r="A5" s="107" t="s">
@@ -11532,16 +11638,16 @@
       <c r="B5" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="184" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="185"/>
     </row>
     <row r="6" spans="1:13" s="59" customFormat="1" ht="101.65" customHeight="1">
       <c r="A6" s="107" t="s">
@@ -11550,16 +11656,16 @@
       <c r="B6" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="183" t="s">
+      <c r="C6" s="184" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="185"/>
     </row>
     <row r="7" spans="1:13" s="59" customFormat="1" ht="243.4" customHeight="1">
       <c r="A7" s="107" t="s">
@@ -11568,16 +11674,16 @@
       <c r="B7" s="109" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="183" t="s">
+      <c r="C7" s="184" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="185"/>
     </row>
     <row r="8" spans="1:13" s="59" customFormat="1" ht="28.15" customHeight="1">
       <c r="A8" s="107" t="s">
@@ -11586,16 +11692,16 @@
       <c r="B8" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="183" t="s">
+      <c r="C8" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="185"/>
     </row>
     <row r="9" spans="1:13" s="59" customFormat="1" ht="33.4" customHeight="1">
       <c r="A9" s="107" t="s">
@@ -11604,16 +11710,16 @@
       <c r="B9" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="183" t="s">
+      <c r="C9" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="185"/>
     </row>
     <row r="10" spans="1:13" s="59" customFormat="1" ht="28.9" customHeight="1">
       <c r="A10" s="107" t="s">
@@ -11622,16 +11728,16 @@
       <c r="B10" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="184" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="184"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="185"/>
     </row>
     <row r="11" spans="1:13" s="59" customFormat="1" ht="43.5" customHeight="1">
       <c r="A11" s="107" t="s">
@@ -11640,17 +11746,17 @@
       <c r="B11" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="183" t="str">
+      <c r="C11" s="184" t="str">
         <f>'PL(2_2)'!D20</f>
         <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
       </c>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="185"/>
       <c r="L11" s="59" t="s">
         <v>183</v>
       </c>
@@ -12027,17 +12133,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C11:J11"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C11:J11"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -12072,46 +12178,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="91.15" customHeight="1" thickBot="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="186" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
     </row>
     <row r="2" spans="1:13" ht="32.65" customHeight="1">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="187" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="188"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="189"/>
     </row>
     <row r="3" spans="1:13" ht="28.15" customHeight="1">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="190" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="191"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="192"/>
     </row>
     <row r="4" spans="1:13" s="59" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="105" t="s">
@@ -12120,16 +12226,16 @@
       <c r="B4" s="106" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="194"/>
+      <c r="I4" s="194"/>
+      <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:13" s="59" customFormat="1" ht="55.5" customHeight="1">
       <c r="A5" s="107" t="s">
@@ -12138,16 +12244,16 @@
       <c r="B5" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="184" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="185"/>
     </row>
     <row r="6" spans="1:13" s="59" customFormat="1" ht="101.65" customHeight="1">
       <c r="A6" s="107" t="s">
@@ -12156,16 +12262,16 @@
       <c r="B6" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="183" t="s">
+      <c r="C6" s="184" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="185"/>
     </row>
     <row r="7" spans="1:13" s="59" customFormat="1" ht="243.4" customHeight="1">
       <c r="A7" s="107" t="s">
@@ -12174,16 +12280,16 @@
       <c r="B7" s="109" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="183" t="s">
+      <c r="C7" s="184" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="185"/>
     </row>
     <row r="8" spans="1:13" s="59" customFormat="1" ht="28.15" customHeight="1">
       <c r="A8" s="107" t="s">
@@ -12192,16 +12298,16 @@
       <c r="B8" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="183" t="s">
+      <c r="C8" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="185"/>
     </row>
     <row r="9" spans="1:13" s="59" customFormat="1" ht="33.4" customHeight="1">
       <c r="A9" s="107" t="s">
@@ -12210,16 +12316,16 @@
       <c r="B9" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="183" t="s">
+      <c r="C9" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="185"/>
     </row>
     <row r="10" spans="1:13" s="59" customFormat="1" ht="28.9" customHeight="1">
       <c r="A10" s="107" t="s">
@@ -12228,16 +12334,16 @@
       <c r="B10" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="184" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="184"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="185"/>
     </row>
     <row r="11" spans="1:13" s="59" customFormat="1" ht="43.5" customHeight="1">
       <c r="A11" s="107" t="s">
@@ -12246,17 +12352,17 @@
       <c r="B11" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="183" t="str">
+      <c r="C11" s="184" t="str">
         <f>'PL(2_2)'!D21</f>
         <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
       </c>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="185"/>
       <c r="L11" s="59" t="s">
         <v>183</v>
       </c>
@@ -12635,17 +12741,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C11:J11"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C11:J11"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -12680,46 +12786,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="91.15" customHeight="1" thickBot="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="186" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
     </row>
     <row r="2" spans="1:13" ht="32.65" customHeight="1">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="187" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="188"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="189"/>
     </row>
     <row r="3" spans="1:13" ht="28.15" customHeight="1">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="190" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="191"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="192"/>
     </row>
     <row r="4" spans="1:13" s="59" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="105" t="s">
@@ -12728,16 +12834,16 @@
       <c r="B4" s="106" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="194"/>
+      <c r="I4" s="194"/>
+      <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:13" s="59" customFormat="1" ht="55.5" customHeight="1">
       <c r="A5" s="107" t="s">
@@ -12746,16 +12852,16 @@
       <c r="B5" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="184" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="185"/>
     </row>
     <row r="6" spans="1:13" s="59" customFormat="1" ht="101.65" customHeight="1">
       <c r="A6" s="107" t="s">
@@ -12764,16 +12870,16 @@
       <c r="B6" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="183" t="s">
+      <c r="C6" s="184" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="185"/>
     </row>
     <row r="7" spans="1:13" s="59" customFormat="1" ht="243.4" customHeight="1">
       <c r="A7" s="107" t="s">
@@ -12782,16 +12888,16 @@
       <c r="B7" s="109" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="183" t="s">
+      <c r="C7" s="184" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="185"/>
     </row>
     <row r="8" spans="1:13" s="59" customFormat="1" ht="28.15" customHeight="1">
       <c r="A8" s="107" t="s">
@@ -12800,16 +12906,16 @@
       <c r="B8" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="183" t="s">
+      <c r="C8" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="185"/>
     </row>
     <row r="9" spans="1:13" s="59" customFormat="1" ht="33.4" customHeight="1">
       <c r="A9" s="107" t="s">
@@ -12818,16 +12924,16 @@
       <c r="B9" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="183" t="s">
+      <c r="C9" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="185"/>
     </row>
     <row r="10" spans="1:13" s="59" customFormat="1" ht="28.9" customHeight="1">
       <c r="A10" s="107" t="s">
@@ -12836,16 +12942,16 @@
       <c r="B10" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="184" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="184"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="185"/>
     </row>
     <row r="11" spans="1:13" s="59" customFormat="1" ht="43.5" customHeight="1">
       <c r="A11" s="107" t="s">
@@ -12854,17 +12960,17 @@
       <c r="B11" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="183" t="str">
+      <c r="C11" s="184" t="str">
         <f>'PL(2_2)'!D22</f>
         <v>HRSG Embeded Material (Anchor Bolt/Nut/Washer)</v>
       </c>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="185"/>
       <c r="L11" s="59" t="s">
         <v>183</v>
       </c>
@@ -13243,17 +13349,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C11:J11"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C11:J11"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -13288,46 +13394,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="91.15" customHeight="1" thickBot="1">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="186" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
     </row>
     <row r="2" spans="1:13" ht="32.65" customHeight="1">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="187" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="188"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="189"/>
     </row>
     <row r="3" spans="1:13" ht="28.15" customHeight="1">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="190" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="191"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="192"/>
     </row>
     <row r="4" spans="1:13" s="59" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="105" t="s">
@@ -13336,16 +13442,16 @@
       <c r="B4" s="106" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="194"/>
+      <c r="I4" s="194"/>
+      <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:13" s="59" customFormat="1" ht="55.5" customHeight="1">
       <c r="A5" s="107" t="s">
@@ -13354,16 +13460,16 @@
       <c r="B5" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="184" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="185"/>
     </row>
     <row r="6" spans="1:13" s="59" customFormat="1" ht="101.65" customHeight="1">
       <c r="A6" s="107" t="s">
@@ -13372,16 +13478,16 @@
       <c r="B6" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="183" t="s">
+      <c r="C6" s="184" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="185"/>
     </row>
     <row r="7" spans="1:13" s="59" customFormat="1" ht="243.4" customHeight="1">
       <c r="A7" s="107" t="s">
@@ -13390,16 +13496,16 @@
       <c r="B7" s="109" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="183" t="s">
+      <c r="C7" s="184" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="185"/>
     </row>
     <row r="8" spans="1:13" s="59" customFormat="1" ht="28.15" customHeight="1">
       <c r="A8" s="107" t="s">
@@ -13408,16 +13514,16 @@
       <c r="B8" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="183" t="s">
+      <c r="C8" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="183"/>
-      <c r="H8" s="183"/>
-      <c r="I8" s="183"/>
-      <c r="J8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="185"/>
     </row>
     <row r="9" spans="1:13" s="59" customFormat="1" ht="33.4" customHeight="1">
       <c r="A9" s="107" t="s">
@@ -13426,16 +13532,16 @@
       <c r="B9" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="183" t="s">
+      <c r="C9" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="185"/>
     </row>
     <row r="10" spans="1:13" s="59" customFormat="1" ht="28.9" customHeight="1">
       <c r="A10" s="107" t="s">
@@ -13444,16 +13550,16 @@
       <c r="B10" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="184" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="184"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="185"/>
     </row>
     <row r="11" spans="1:13" s="59" customFormat="1" ht="43.5" customHeight="1">
       <c r="A11" s="107" t="s">
@@ -13462,17 +13568,17 @@
       <c r="B11" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="183" t="str">
+      <c r="C11" s="184" t="str">
         <f>'PL(2_2)'!D23</f>
         <v>HRSG Embeded Material (Spare)</v>
       </c>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="184"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="185"/>
       <c r="L11" s="59" t="s">
         <v>183</v>
       </c>
@@ -13849,17 +13955,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C11:J11"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C11:J11"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -14098,15 +14204,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a4d5cc5e-dfa1-4e82-94a9-1981df698304" xsi:nil="true"/>
@@ -14115,6 +14212,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14131,14 +14237,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD118D43-B7CD-45F3-8174-31C6C469D825}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D6C71D9-1122-41BE-8046-842F0AE68963}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14151,6 +14249,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD118D43-B7CD-45F3-8174-31C6C469D825}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9d1b3610-9ab0-42d5-93aa-46150d723d87}" enabled="0" method="" siteId="{9d1b3610-9ab0-42d5-93aa-46150d723d87}" removed="1"/>
